--- a/预推免院校/汇总.xlsx
+++ b/预推免院校/汇总.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1288,7 +1288,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1313,13 +1313,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1421,18 +1424,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1448,6 +1445,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="58" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1457,22 +1457,37 @@
     <xf numFmtId="58" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1792,513 +1807,513 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="17.7909090909091" customWidth="1"/>
-    <col min="3" max="3" width="31.0454545454545" customWidth="1"/>
+    <col min="2" max="2" width="17.7916666666667" customWidth="1"/>
+    <col min="3" max="3" width="31.0416666666667" customWidth="1"/>
     <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="5" max="5" width="51.8090909090909" customWidth="1"/>
-    <col min="6" max="6" width="17.4818181818182" customWidth="1"/>
-    <col min="7" max="7" width="16.7818181818182" customWidth="1"/>
-    <col min="8" max="8" width="14.1272727272727"/>
+    <col min="5" max="5" width="51.8083333333333" customWidth="1"/>
+    <col min="6" max="6" width="17.4833333333333" customWidth="1"/>
+    <col min="7" max="7" width="16.7833333333333" customWidth="1"/>
+    <col min="8" max="8" width="14.125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:13">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="16">
         <v>45840</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="18">
         <v>20263300215</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="13"/>
+      <c r="M2" s="14"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:13">
-      <c r="A3" s="18">
+      <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="21">
         <v>45842</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="21">
         <v>45900</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="J3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="K3" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:13">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <v>4</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="16">
         <v>45848</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="16">
         <v>45918</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="13"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" s="3" customFormat="1" spans="1:13">
-      <c r="A5" s="22">
+      <c r="A5" s="23">
         <v>5</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="60" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:13">
-      <c r="A6" s="22">
+      <c r="A6" s="23">
         <v>6</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23" t="s">
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="60" t="s">
+      <c r="J6" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
     </row>
     <row r="7" s="4" customFormat="1" spans="1:13">
-      <c r="A7" s="25">
+      <c r="A7" s="26">
         <v>7</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="28">
         <v>45874</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="28">
         <v>45897</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="29">
         <v>20263300074</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="I7" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="26" t="s">
+      <c r="J7" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
     </row>
     <row r="8" s="4" customFormat="1" spans="1:13">
-      <c r="A8" s="25">
+      <c r="A8" s="26">
         <v>8</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <v>45864</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="28">
         <v>45920</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="29">
         <v>26002158</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="I8" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="26" t="s">
+      <c r="J8" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:13">
-      <c r="A9" s="22">
+      <c r="A9" s="23">
         <v>9</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>45867</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <v>45879</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="24">
         <v>20263308927</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="61" t="s">
+      <c r="J9" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
     </row>
     <row r="10" s="5" customFormat="1" spans="1:13">
-      <c r="A10" s="31">
+      <c r="A10" s="32">
         <v>10</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="34">
         <v>45857</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="34">
         <v>45901</v>
       </c>
-      <c r="H10" s="34" t="s">
+      <c r="H10" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="34" t="s">
+      <c r="I10" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="32" t="s">
+      <c r="J10" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
     </row>
     <row r="11" s="6" customFormat="1" spans="1:13">
-      <c r="A11" s="35">
+      <c r="A11" s="36">
         <v>11</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="E11" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37" t="s">
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="36" t="s">
+      <c r="J11" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="K11" s="35" t="s">
+      <c r="K11" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="35" t="s">
+      <c r="L11" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="35" t="s">
+      <c r="M11" s="36" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:13">
-      <c r="A12" s="18">
+      <c r="A12" s="19">
         <v>12</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="21" t="s">
+      <c r="E12" s="20"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="I12" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="19" t="s">
+      <c r="J12" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
     </row>
     <row r="13" s="7" customFormat="1" spans="1:13">
-      <c r="A13" s="39">
+      <c r="A13" s="40">
         <v>13</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40">
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41">
         <v>20263301375</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="41" t="s">
         <v>18</v>
       </c>
       <c r="J13" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="41">
+      <c r="A14" s="42">
         <v>14</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="43">
         <v>45871</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="43">
         <v>45919</v>
       </c>
-      <c r="H14" s="43">
+      <c r="H14" s="44">
         <v>20262200196</v>
       </c>
-      <c r="I14" s="43" t="s">
+      <c r="I14" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="24" t="s">
+      <c r="J14" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
     </row>
     <row r="15" s="8" customFormat="1" spans="1:13">
-      <c r="A15" s="44">
+      <c r="A15" s="45">
         <v>15</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="20" t="s">
         <v>76</v>
       </c>
       <c r="F15" s="46">
@@ -2307,198 +2322,198 @@
       <c r="G15" s="46">
         <v>45910</v>
       </c>
-      <c r="H15" s="47" t="s">
+      <c r="H15" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="I15" s="47" t="s">
+      <c r="I15" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="45" t="s">
+      <c r="J15" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="45"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="41">
+      <c r="A16" s="42">
         <v>16</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="41" t="s">
+      <c r="D16" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="48">
+      <c r="F16" s="47">
         <v>45855</v>
       </c>
-      <c r="G16" s="48">
+      <c r="G16" s="47">
         <v>45897</v>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="42">
         <v>202601506</v>
       </c>
-      <c r="I16" s="41" t="s">
+      <c r="I16" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="24" t="s">
+      <c r="J16" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
     </row>
     <row r="17" s="4" customFormat="1" spans="1:13">
-      <c r="A17" s="25">
+      <c r="A17" s="26">
         <v>17</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="E17" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="48">
         <v>45886</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="48">
         <v>45916</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <v>20263312838</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="I17" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="26" t="s">
+      <c r="J17" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
     </row>
     <row r="18" s="9" customFormat="1" spans="1:13">
-      <c r="A18" s="50">
+      <c r="A18" s="49">
         <v>18</v>
       </c>
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="50" t="s">
+      <c r="D18" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50" t="s">
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="I18" s="50" t="s">
+      <c r="I18" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="51" t="s">
+      <c r="J18" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="K18" s="50"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="50"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="49"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="41">
+      <c r="A19" s="42">
         <v>19</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="D19" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="52" t="s">
+      <c r="E19" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="48">
+      <c r="F19" s="47">
         <v>45901</v>
       </c>
-      <c r="G19" s="48">
+      <c r="G19" s="47">
         <v>45915</v>
       </c>
-      <c r="H19" s="41" t="s">
+      <c r="H19" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="I19" s="41" t="s">
+      <c r="I19" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="24" t="s">
+      <c r="J19" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="41">
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+    </row>
+    <row r="20" s="10" customFormat="1" spans="1:13">
+      <c r="A20" s="52">
         <v>20</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D20" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41" t="s">
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="I20" s="41" t="s">
+      <c r="I20" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="24" t="s">
+      <c r="J20" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="K20" s="41"/>
-      <c r="L20" s="41"/>
-      <c r="M20" s="41"/>
+      <c r="K20" s="52"/>
+      <c r="L20" s="52"/>
+      <c r="M20" s="52"/>
     </row>
     <row r="21" s="9" customFormat="1" spans="1:13">
-      <c r="A21" s="50">
+      <c r="A21" s="49">
         <v>21</v>
       </c>
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="50" t="s">
+      <c r="D21" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="51" t="s">
+      <c r="E21" s="50" t="s">
         <v>96</v>
       </c>
       <c r="F21" s="53">
@@ -2507,135 +2522,135 @@
       <c r="G21" s="53">
         <v>45912</v>
       </c>
-      <c r="H21" s="50" t="s">
+      <c r="H21" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="50" t="s">
+      <c r="I21" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="J21" s="51" t="s">
+      <c r="J21" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="K21" s="50"/>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="41">
+      <c r="A22" s="42">
         <v>19</v>
       </c>
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="41" t="s">
+      <c r="D22" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="52" t="s">
+      <c r="E22" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="47">
         <v>45901</v>
       </c>
-      <c r="G22" s="48">
+      <c r="G22" s="47">
         <v>45915</v>
       </c>
-      <c r="H22" s="41" t="s">
+      <c r="H22" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="I22" s="41" t="s">
+      <c r="I22" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="J22" s="24" t="s">
+      <c r="J22" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="K22" s="41"/>
-      <c r="L22" s="41"/>
-      <c r="M22" s="41"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="41">
+      <c r="A23" s="42">
         <v>19</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="D23" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="F23" s="48">
+      <c r="F23" s="47">
         <v>45901</v>
       </c>
-      <c r="G23" s="48">
+      <c r="G23" s="47">
         <v>45915</v>
       </c>
-      <c r="H23" s="41" t="s">
+      <c r="H23" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="I23" s="41" t="s">
+      <c r="I23" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="J23" s="24" t="s">
+      <c r="J23" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="K23" s="41"/>
-      <c r="L23" s="41"/>
-      <c r="M23" s="41"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="41">
+      <c r="A24" s="42">
         <v>24</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="41" t="s">
+      <c r="D24" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="52" t="s">
+      <c r="E24" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="F24" s="48">
+      <c r="F24" s="47">
         <v>45871</v>
       </c>
-      <c r="G24" s="48">
+      <c r="G24" s="47">
         <v>45903</v>
       </c>
-      <c r="H24" s="41">
+      <c r="H24" s="42">
         <v>20253305016</v>
       </c>
-      <c r="I24" s="41" t="s">
+      <c r="I24" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="J24" s="24" t="s">
+      <c r="J24" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="K24" s="41"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="41"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="42"/>
     </row>
     <row r="25" s="7" customFormat="1" spans="1:13">
-      <c r="A25" s="39">
+      <c r="A25" s="40">
         <v>25</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="39" t="s">
+      <c r="D25" s="40" t="s">
         <v>105</v>
       </c>
       <c r="E25" s="54" t="s">
@@ -2647,25 +2662,25 @@
       <c r="G25" s="55">
         <v>45912</v>
       </c>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="40"/>
     </row>
     <row r="26" s="9" customFormat="1" spans="1:13">
-      <c r="A26" s="50">
+      <c r="A26" s="49">
         <v>26</v>
       </c>
-      <c r="B26" s="50" t="s">
+      <c r="B26" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50" t="s">
+      <c r="C26" s="49"/>
+      <c r="D26" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="51" t="s">
+      <c r="E26" s="50" t="s">
         <v>108</v>
       </c>
       <c r="F26" s="53">
@@ -2674,203 +2689,203 @@
       <c r="G26" s="53">
         <v>45919</v>
       </c>
-      <c r="H26" s="50" t="s">
+      <c r="H26" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="I26" s="50" t="s">
+      <c r="I26" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J26" s="51" t="s">
+      <c r="J26" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="K26" s="50"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="50"/>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="41">
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+    </row>
+    <row r="27" s="10" customFormat="1" spans="1:13">
+      <c r="A27" s="52">
         <v>27</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="D27" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="48">
+      <c r="F27" s="56">
         <v>45902</v>
       </c>
-      <c r="G27" s="48">
+      <c r="G27" s="56">
         <v>45915</v>
       </c>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="24" t="s">
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
-    </row>
-    <row r="28" s="9" customFormat="1" spans="1:13">
-      <c r="A28" s="50">
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
+    </row>
+    <row r="28" s="6" customFormat="1" spans="1:13">
+      <c r="A28" s="36">
         <v>28</v>
       </c>
-      <c r="B28" s="50" t="s">
+      <c r="B28" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="C28" s="50" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="50" t="s">
+      <c r="C28" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="51" t="s">
+      <c r="E28" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="41" t="s">
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="41" t="s">
+      <c r="I28" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="J28" s="51" t="s">
+      <c r="J28" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="50"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:13">
-      <c r="A29" s="13">
+      <c r="A29" s="14">
         <v>29</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="56" t="s">
+      <c r="E29" s="57" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="57">
+      <c r="F29" s="58">
         <v>45902</v>
       </c>
-      <c r="G29" s="57">
+      <c r="G29" s="58">
         <v>45915</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H29" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="13" t="s">
+      <c r="I29" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="J29" s="14" t="s">
+      <c r="J29" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="K29" s="13" t="s">
+      <c r="K29" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="L29" s="13" t="s">
+      <c r="L29" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="M29" s="13"/>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="41">
+      <c r="M29" s="14"/>
+    </row>
+    <row r="30" s="11" customFormat="1" spans="1:13">
+      <c r="A30" s="59">
         <v>30</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="41" t="s">
+      <c r="D30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="52" t="s">
+      <c r="E30" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="F30" s="48">
+      <c r="F30" s="60">
         <v>45902</v>
       </c>
-      <c r="G30" s="48">
+      <c r="G30" s="60">
         <v>45910</v>
       </c>
-      <c r="H30" s="41" t="s">
+      <c r="H30" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="I30" s="41" t="s">
+      <c r="I30" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="J30" s="24" t="s">
+      <c r="J30" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="K30" s="41"/>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
-    </row>
-    <row r="31" s="9" customFormat="1" spans="1:13">
-      <c r="A31" s="50">
+      <c r="K30" s="59"/>
+      <c r="L30" s="59"/>
+      <c r="M30" s="59"/>
+    </row>
+    <row r="31" s="4" customFormat="1" spans="1:13">
+      <c r="A31" s="26">
         <v>31</v>
       </c>
-      <c r="B31" s="50" t="s">
+      <c r="B31" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="50" t="s">
+      <c r="C31" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="50" t="s">
+      <c r="D31" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="E31" s="51" t="s">
+      <c r="E31" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="F31" s="53">
+      <c r="F31" s="48">
         <v>45906</v>
       </c>
-      <c r="G31" s="53">
+      <c r="G31" s="48">
         <v>45910</v>
       </c>
-      <c r="H31" s="50" t="s">
+      <c r="H31" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="I31" s="50" t="s">
+      <c r="I31" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="J31" s="51" t="s">
+      <c r="J31" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="K31" s="50"/>
-      <c r="L31" s="50"/>
-      <c r="M31" s="50" t="s">
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="32" s="7" customFormat="1" spans="1:13">
-      <c r="A32" s="39">
+      <c r="A32" s="40">
         <v>32</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="39" t="s">
+      <c r="D32" s="40" t="s">
         <v>105</v>
       </c>
       <c r="E32" s="54" t="s">
@@ -2882,230 +2897,230 @@
       <c r="G32" s="55">
         <v>45915</v>
       </c>
-      <c r="H32" s="39">
+      <c r="H32" s="40">
         <v>20263304452</v>
       </c>
-      <c r="I32" s="39" t="s">
+      <c r="I32" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="J32" s="52" t="s">
+      <c r="J32" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="K32" s="39"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="39"/>
+      <c r="K32" s="40"/>
+      <c r="L32" s="40"/>
+      <c r="M32" s="40"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:13">
-      <c r="A33" s="13">
+      <c r="A33" s="14">
         <v>33</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E33" s="58" t="s">
+      <c r="E33" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="F33" s="57">
+      <c r="F33" s="58">
         <v>45905</v>
       </c>
-      <c r="G33" s="57">
+      <c r="G33" s="58">
         <v>45909</v>
       </c>
-      <c r="H33" s="13">
+      <c r="H33" s="14">
         <v>20263311417</v>
       </c>
-      <c r="I33" s="13" t="s">
+      <c r="I33" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="J33" s="58" t="s">
+      <c r="J33" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="K33" s="13" t="s">
+      <c r="K33" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="L33" s="13" t="s">
+      <c r="L33" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="M33" s="13"/>
+      <c r="M33" s="14"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="41">
+      <c r="A34" s="42">
         <v>34</v>
       </c>
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="D34" s="41"/>
-      <c r="E34" s="52" t="s">
+      <c r="D34" s="42"/>
+      <c r="E34" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="F34" s="48">
+      <c r="F34" s="47">
         <v>45880</v>
       </c>
-      <c r="G34" s="48">
+      <c r="G34" s="47">
         <v>45910</v>
       </c>
-      <c r="H34" s="41" t="s">
+      <c r="H34" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="I34" s="41" t="s">
+      <c r="I34" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="J34" s="24" t="s">
+      <c r="J34" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="42"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:13">
-      <c r="A35" s="13">
+      <c r="A35" s="14">
         <v>35</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13">
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14">
         <v>202608849</v>
       </c>
-      <c r="I35" s="13" t="s">
+      <c r="I35" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="J35" s="14" t="s">
+      <c r="J35" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="K35" s="13" t="s">
+      <c r="K35" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="L35" s="13" t="s">
+      <c r="L35" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="M35" s="13"/>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="41">
+      <c r="M35" s="14"/>
+    </row>
+    <row r="36" s="11" customFormat="1" spans="1:13">
+      <c r="A36" s="59">
         <v>36</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="41" t="s">
+      <c r="C36" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="41" t="s">
+      <c r="D36" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="F36" s="48">
+      <c r="F36" s="60">
         <v>45904</v>
       </c>
-      <c r="G36" s="48">
+      <c r="G36" s="60">
         <v>45912</v>
       </c>
-      <c r="H36" s="41">
+      <c r="H36" s="59">
         <v>20263327091</v>
       </c>
-      <c r="I36" s="41" t="s">
+      <c r="I36" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="J36" s="24" t="s">
+      <c r="J36" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="K36" s="41"/>
-      <c r="L36" s="41"/>
-      <c r="M36" s="41"/>
-    </row>
-    <row r="37" s="10" customFormat="1" spans="1:13">
-      <c r="A37" s="59">
+      <c r="K36" s="59"/>
+      <c r="L36" s="59"/>
+      <c r="M36" s="59"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:13">
+      <c r="A37" s="14">
         <v>37</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="13" t="s">
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="I37" s="13" t="s">
+      <c r="I37" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="J37" s="56" t="s">
+      <c r="J37" s="57" t="s">
         <v>147</v>
       </c>
-      <c r="K37" s="59"/>
-      <c r="L37" s="59"/>
-      <c r="M37" s="59"/>
-    </row>
-    <row r="38" s="7" customFormat="1" spans="1:15">
-      <c r="A38" s="41">
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+    </row>
+    <row r="38" s="6" customFormat="1" spans="1:15">
+      <c r="A38" s="62">
         <v>38</v>
       </c>
-      <c r="B38" s="41" t="s">
+      <c r="B38" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="C38" s="41" t="s">
+      <c r="C38" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="D38" s="41" t="s">
+      <c r="D38" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E38" s="52" t="s">
+      <c r="E38" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="F38" s="48">
+      <c r="F38" s="63">
         <v>45904</v>
       </c>
-      <c r="G38" s="48">
+      <c r="G38" s="63">
         <v>45913</v>
       </c>
-      <c r="H38" s="41"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="41"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="41"/>
-      <c r="N38"/>
-      <c r="O38"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="62"/>
+      <c r="J38" s="62"/>
+      <c r="K38" s="62"/>
+      <c r="L38" s="62"/>
+      <c r="M38" s="62"/>
+      <c r="N38" s="66"/>
+      <c r="O38" s="66"/>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="41">
+      <c r="A39" s="42">
         <v>39</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="C39" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D39" s="39" t="s">
+      <c r="D39" s="40" t="s">
         <v>105</v>
       </c>
       <c r="E39" s="54" t="s">
@@ -3117,573 +3132,573 @@
       <c r="G39" s="55">
         <v>45915</v>
       </c>
-      <c r="H39" s="39">
+      <c r="H39" s="40">
         <v>202602944</v>
       </c>
       <c r="I39" s="54" t="s">
         <v>153</v>
       </c>
-      <c r="J39" s="39"/>
-      <c r="K39" s="39"/>
-      <c r="L39" s="39"/>
-      <c r="M39" s="39"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="40"/>
       <c r="N39" s="7"/>
       <c r="O39" s="7"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:13">
-      <c r="A40" s="13">
+      <c r="A40" s="14">
         <v>40</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="F40" s="57">
+      <c r="F40" s="58">
         <v>45908</v>
       </c>
-      <c r="G40" s="57">
+      <c r="G40" s="58">
         <v>45921</v>
       </c>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="14" t="s">
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="K40" s="13"/>
-      <c r="L40" s="13"/>
-      <c r="M40" s="13"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
     </row>
     <row r="41" s="7" customFormat="1" spans="1:15">
-      <c r="A41" s="41">
+      <c r="A41" s="42">
         <v>41</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="C41" s="41" t="s">
+      <c r="C41" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="D41" s="41" t="s">
+      <c r="D41" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E41" s="52" t="s">
+      <c r="E41" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="F41" s="48">
+      <c r="F41" s="47">
         <v>45910</v>
       </c>
-      <c r="G41" s="48">
+      <c r="G41" s="47">
         <v>45916</v>
       </c>
-      <c r="H41" s="41" t="s">
+      <c r="H41" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="41" t="s">
+      <c r="I41" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="J41" s="24" t="s">
+      <c r="J41" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="K41" s="41"/>
-      <c r="L41" s="41"/>
-      <c r="M41" s="41"/>
+      <c r="K41" s="42"/>
+      <c r="L41" s="42"/>
+      <c r="M41" s="42"/>
       <c r="N41"/>
       <c r="O41"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="41">
+      <c r="A42" s="42">
         <v>42</v>
       </c>
-      <c r="B42" s="41" t="s">
+      <c r="B42" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="C42" s="41" t="s">
+      <c r="C42" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="D42" s="41" t="s">
+      <c r="D42" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E42" s="52" t="s">
+      <c r="E42" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="F42" s="48">
+      <c r="F42" s="47">
         <v>45909</v>
       </c>
-      <c r="G42" s="48">
+      <c r="G42" s="47">
         <v>45922</v>
       </c>
-      <c r="H42" s="41">
+      <c r="H42" s="42">
         <v>202601040</v>
       </c>
-      <c r="I42" s="41" t="s">
+      <c r="I42" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J42" s="52" t="s">
+      <c r="J42" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="K42" s="41"/>
-      <c r="L42" s="41"/>
-      <c r="M42" s="41"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:13">
-      <c r="A43" s="13">
+      <c r="A43" s="14">
         <v>43</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13">
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14">
         <v>20263309395</v>
       </c>
-      <c r="I43" s="13" t="s">
+      <c r="I43" s="14" t="s">
         <v>18</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="K43" s="13"/>
-      <c r="L43" s="13"/>
-      <c r="M43" s="13"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="41">
+      <c r="A44" s="42">
         <v>44</v>
       </c>
-      <c r="B44" s="41" t="s">
+      <c r="B44" s="42" t="s">
         <v>167</v>
       </c>
-      <c r="C44" s="41" t="s">
+      <c r="C44" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="D44" s="41" t="s">
+      <c r="D44" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
-      <c r="L44" s="41"/>
-      <c r="M44" s="41"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="42"/>
+      <c r="M44" s="42"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="41">
+      <c r="A45" s="42">
         <v>45</v>
       </c>
-      <c r="B45" s="41"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="42"/>
+      <c r="M45" s="42"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="41">
+      <c r="A46" s="42">
         <v>46</v>
       </c>
-      <c r="B46" s="41"/>
-      <c r="C46" s="41"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="41"/>
-      <c r="M46" s="41"/>
+      <c r="B46" s="42"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="42"/>
+      <c r="L46" s="42"/>
+      <c r="M46" s="42"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="41">
+      <c r="A47" s="42">
         <v>47</v>
       </c>
-      <c r="B47" s="41"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="41"/>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="41"/>
-      <c r="M47" s="41"/>
+      <c r="B47" s="42"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="42"/>
+      <c r="L47" s="42"/>
+      <c r="M47" s="42"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="41">
+      <c r="A48" s="42">
         <v>48</v>
       </c>
-      <c r="B48" s="41"/>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="41"/>
-      <c r="J48" s="41"/>
-      <c r="K48" s="41"/>
-      <c r="L48" s="41"/>
-      <c r="M48" s="41"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="42"/>
+      <c r="L48" s="42"/>
+      <c r="M48" s="42"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="41">
+      <c r="A49" s="42">
         <v>49</v>
       </c>
-      <c r="B49" s="41"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
-      <c r="M49" s="41"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="42"/>
+      <c r="L49" s="42"/>
+      <c r="M49" s="42"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="41"/>
-      <c r="B50" s="41"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="41"/>
-      <c r="M50" s="41"/>
+      <c r="A50" s="42"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="42"/>
+      <c r="L50" s="42"/>
+      <c r="M50" s="42"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="41"/>
-      <c r="B51" s="41"/>
-      <c r="C51" s="41"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="41"/>
-      <c r="I51" s="41"/>
-      <c r="J51" s="41"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="41"/>
-      <c r="M51" s="41"/>
+      <c r="A51" s="42"/>
+      <c r="B51" s="42"/>
+      <c r="C51" s="42"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
+      <c r="K51" s="42"/>
+      <c r="L51" s="42"/>
+      <c r="M51" s="42"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="41"/>
-      <c r="B52" s="41"/>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="41"/>
-      <c r="J52" s="41"/>
-      <c r="K52" s="41"/>
-      <c r="L52" s="41"/>
-      <c r="M52" s="41"/>
+      <c r="A52" s="42"/>
+      <c r="B52" s="42"/>
+      <c r="C52" s="42"/>
+      <c r="D52" s="42"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="42"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="42"/>
+      <c r="K52" s="42"/>
+      <c r="L52" s="42"/>
+      <c r="M52" s="42"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="41"/>
-      <c r="B53" s="41"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="41"/>
-      <c r="J53" s="41"/>
-      <c r="K53" s="41"/>
-      <c r="L53" s="41"/>
-      <c r="M53" s="41"/>
+      <c r="A53" s="42"/>
+      <c r="B53" s="42"/>
+      <c r="C53" s="42"/>
+      <c r="D53" s="42"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="42"/>
+      <c r="H53" s="42"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="42"/>
+      <c r="K53" s="42"/>
+      <c r="L53" s="42"/>
+      <c r="M53" s="42"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="41"/>
-      <c r="B54" s="41"/>
-      <c r="C54" s="41"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="41"/>
-      <c r="M54" s="41"/>
+      <c r="A54" s="42"/>
+      <c r="B54" s="42"/>
+      <c r="C54" s="42"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="42"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="42"/>
+      <c r="L54" s="42"/>
+      <c r="M54" s="42"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="41"/>
-      <c r="B55" s="41"/>
-      <c r="C55" s="41"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="41"/>
-      <c r="J55" s="41"/>
-      <c r="K55" s="41"/>
-      <c r="L55" s="41"/>
-      <c r="M55" s="41"/>
+      <c r="A55" s="42"/>
+      <c r="B55" s="42"/>
+      <c r="C55" s="42"/>
+      <c r="D55" s="42"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="42"/>
+      <c r="H55" s="42"/>
+      <c r="I55" s="42"/>
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
+      <c r="L55" s="42"/>
+      <c r="M55" s="42"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="41"/>
-      <c r="B56" s="41"/>
-      <c r="C56" s="41"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="41"/>
-      <c r="I56" s="41"/>
-      <c r="J56" s="41"/>
-      <c r="K56" s="41"/>
-      <c r="L56" s="41"/>
-      <c r="M56" s="41"/>
+      <c r="A56" s="42"/>
+      <c r="B56" s="42"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="42"/>
+      <c r="E56" s="42"/>
+      <c r="F56" s="42"/>
+      <c r="G56" s="42"/>
+      <c r="H56" s="42"/>
+      <c r="I56" s="42"/>
+      <c r="J56" s="42"/>
+      <c r="K56" s="42"/>
+      <c r="L56" s="42"/>
+      <c r="M56" s="42"/>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="41"/>
-      <c r="B57" s="41"/>
-      <c r="C57" s="41"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="41"/>
-      <c r="J57" s="41"/>
-      <c r="K57" s="41"/>
-      <c r="L57" s="41"/>
-      <c r="M57" s="41"/>
+      <c r="A57" s="42"/>
+      <c r="B57" s="42"/>
+      <c r="C57" s="42"/>
+      <c r="D57" s="42"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="42"/>
+      <c r="H57" s="42"/>
+      <c r="I57" s="42"/>
+      <c r="J57" s="42"/>
+      <c r="K57" s="42"/>
+      <c r="L57" s="42"/>
+      <c r="M57" s="42"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="41"/>
-      <c r="B58" s="41"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
-      <c r="H58" s="41"/>
-      <c r="I58" s="41"/>
-      <c r="J58" s="41"/>
-      <c r="K58" s="41"/>
-      <c r="L58" s="41"/>
-      <c r="M58" s="41"/>
+      <c r="A58" s="42"/>
+      <c r="B58" s="42"/>
+      <c r="C58" s="42"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="42"/>
+      <c r="H58" s="42"/>
+      <c r="I58" s="42"/>
+      <c r="J58" s="42"/>
+      <c r="K58" s="42"/>
+      <c r="L58" s="42"/>
+      <c r="M58" s="42"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="41"/>
-      <c r="B59" s="41"/>
-      <c r="C59" s="41"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="41"/>
-      <c r="H59" s="41"/>
-      <c r="I59" s="41"/>
-      <c r="J59" s="41"/>
-      <c r="K59" s="41"/>
-      <c r="L59" s="41"/>
-      <c r="M59" s="41"/>
+      <c r="A59" s="42"/>
+      <c r="B59" s="42"/>
+      <c r="C59" s="42"/>
+      <c r="D59" s="42"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="42"/>
+      <c r="H59" s="42"/>
+      <c r="I59" s="42"/>
+      <c r="J59" s="42"/>
+      <c r="K59" s="42"/>
+      <c r="L59" s="42"/>
+      <c r="M59" s="42"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="41"/>
-      <c r="B60" s="41"/>
-      <c r="C60" s="41"/>
-      <c r="D60" s="41"/>
-      <c r="E60" s="41"/>
-      <c r="F60" s="41"/>
-      <c r="G60" s="41"/>
-      <c r="H60" s="41"/>
-      <c r="I60" s="41"/>
-      <c r="J60" s="41"/>
-      <c r="K60" s="41"/>
-      <c r="L60" s="41"/>
-      <c r="M60" s="41"/>
+      <c r="A60" s="42"/>
+      <c r="B60" s="42"/>
+      <c r="C60" s="42"/>
+      <c r="D60" s="42"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="42"/>
+      <c r="H60" s="42"/>
+      <c r="I60" s="42"/>
+      <c r="J60" s="42"/>
+      <c r="K60" s="42"/>
+      <c r="L60" s="42"/>
+      <c r="M60" s="42"/>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="41"/>
-      <c r="B61" s="41"/>
-      <c r="C61" s="41"/>
-      <c r="D61" s="41"/>
-      <c r="E61" s="41"/>
-      <c r="F61" s="41"/>
-      <c r="G61" s="41"/>
-      <c r="H61" s="41"/>
-      <c r="I61" s="41"/>
-      <c r="J61" s="41"/>
-      <c r="K61" s="41"/>
-      <c r="L61" s="41"/>
-      <c r="M61" s="41"/>
+      <c r="A61" s="42"/>
+      <c r="B61" s="42"/>
+      <c r="C61" s="42"/>
+      <c r="D61" s="42"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="42"/>
+      <c r="G61" s="42"/>
+      <c r="H61" s="42"/>
+      <c r="I61" s="42"/>
+      <c r="J61" s="42"/>
+      <c r="K61" s="42"/>
+      <c r="L61" s="42"/>
+      <c r="M61" s="42"/>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="41"/>
-      <c r="B62" s="41"/>
-      <c r="C62" s="41"/>
-      <c r="D62" s="41"/>
-      <c r="E62" s="41"/>
-      <c r="F62" s="41"/>
-      <c r="G62" s="41"/>
-      <c r="H62" s="41"/>
-      <c r="I62" s="41"/>
-      <c r="J62" s="41"/>
-      <c r="K62" s="41"/>
-      <c r="L62" s="41"/>
-      <c r="M62" s="41"/>
+      <c r="A62" s="42"/>
+      <c r="B62" s="42"/>
+      <c r="C62" s="42"/>
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="42"/>
+      <c r="H62" s="42"/>
+      <c r="I62" s="42"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
+      <c r="L62" s="42"/>
+      <c r="M62" s="42"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="41"/>
-      <c r="B63" s="41"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="41"/>
-      <c r="H63" s="41"/>
-      <c r="I63" s="41"/>
-      <c r="J63" s="41"/>
-      <c r="K63" s="41"/>
-      <c r="L63" s="41"/>
-      <c r="M63" s="41"/>
+      <c r="A63" s="42"/>
+      <c r="B63" s="42"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="42"/>
+      <c r="H63" s="42"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="42"/>
+      <c r="K63" s="42"/>
+      <c r="L63" s="42"/>
+      <c r="M63" s="42"/>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="41"/>
-      <c r="B64" s="41"/>
-      <c r="C64" s="41"/>
-      <c r="D64" s="41"/>
-      <c r="E64" s="41"/>
-      <c r="F64" s="41"/>
-      <c r="G64" s="41"/>
-      <c r="H64" s="41"/>
-      <c r="I64" s="41"/>
-      <c r="J64" s="41"/>
-      <c r="K64" s="41"/>
-      <c r="L64" s="41"/>
-      <c r="M64" s="41"/>
+      <c r="A64" s="42"/>
+      <c r="B64" s="42"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="42"/>
+      <c r="H64" s="42"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="42"/>
+      <c r="K64" s="42"/>
+      <c r="L64" s="42"/>
+      <c r="M64" s="42"/>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="41"/>
-      <c r="B65" s="41"/>
-      <c r="C65" s="41"/>
-      <c r="D65" s="41"/>
-      <c r="E65" s="41"/>
-      <c r="F65" s="41"/>
-      <c r="G65" s="41"/>
-      <c r="H65" s="41"/>
-      <c r="I65" s="41"/>
-      <c r="J65" s="41"/>
-      <c r="K65" s="41"/>
-      <c r="L65" s="41"/>
-      <c r="M65" s="41"/>
+      <c r="A65" s="42"/>
+      <c r="B65" s="42"/>
+      <c r="C65" s="42"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="42"/>
+      <c r="F65" s="42"/>
+      <c r="G65" s="42"/>
+      <c r="H65" s="42"/>
+      <c r="I65" s="42"/>
+      <c r="J65" s="42"/>
+      <c r="K65" s="42"/>
+      <c r="L65" s="42"/>
+      <c r="M65" s="42"/>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="41"/>
-      <c r="B66" s="41"/>
-      <c r="C66" s="41"/>
-      <c r="D66" s="41"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="41"/>
-      <c r="H66" s="41"/>
-      <c r="I66" s="41"/>
-      <c r="J66" s="41"/>
-      <c r="K66" s="41"/>
-      <c r="L66" s="41"/>
-      <c r="M66" s="41"/>
+      <c r="A66" s="42"/>
+      <c r="B66" s="42"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="42"/>
+      <c r="I66" s="42"/>
+      <c r="J66" s="42"/>
+      <c r="K66" s="42"/>
+      <c r="L66" s="42"/>
+      <c r="M66" s="42"/>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="41"/>
-      <c r="B67" s="41"/>
-      <c r="C67" s="41"/>
-      <c r="D67" s="41"/>
-      <c r="E67" s="41"/>
-      <c r="F67" s="41"/>
-      <c r="G67" s="41"/>
-      <c r="H67" s="41"/>
-      <c r="I67" s="41"/>
-      <c r="J67" s="41"/>
-      <c r="K67" s="41"/>
-      <c r="L67" s="41"/>
-      <c r="M67" s="41"/>
+      <c r="A67" s="42"/>
+      <c r="B67" s="42"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="42"/>
+      <c r="G67" s="42"/>
+      <c r="H67" s="42"/>
+      <c r="I67" s="42"/>
+      <c r="J67" s="42"/>
+      <c r="K67" s="42"/>
+      <c r="L67" s="42"/>
+      <c r="M67" s="42"/>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="41"/>
-      <c r="B68" s="41"/>
-      <c r="C68" s="41"/>
-      <c r="D68" s="41"/>
-      <c r="E68" s="41"/>
-      <c r="F68" s="41"/>
-      <c r="G68" s="41"/>
-      <c r="H68" s="41"/>
-      <c r="I68" s="41"/>
-      <c r="J68" s="41"/>
-      <c r="K68" s="41"/>
-      <c r="L68" s="41"/>
-      <c r="M68" s="41"/>
+      <c r="A68" s="42"/>
+      <c r="B68" s="42"/>
+      <c r="C68" s="42"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="42"/>
+      <c r="I68" s="42"/>
+      <c r="J68" s="42"/>
+      <c r="K68" s="42"/>
+      <c r="L68" s="42"/>
+      <c r="M68" s="42"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="41"/>
-      <c r="B69" s="41"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="41"/>
-      <c r="H69" s="41"/>
-      <c r="I69" s="41"/>
-      <c r="J69" s="41"/>
-      <c r="K69" s="41"/>
-      <c r="L69" s="41"/>
-      <c r="M69" s="41"/>
+      <c r="A69" s="42"/>
+      <c r="B69" s="42"/>
+      <c r="C69" s="42"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="42"/>
+      <c r="I69" s="42"/>
+      <c r="J69" s="42"/>
+      <c r="K69" s="42"/>
+      <c r="L69" s="42"/>
+      <c r="M69" s="42"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="41"/>
-      <c r="B70" s="41"/>
-      <c r="C70" s="41"/>
-      <c r="D70" s="41"/>
-      <c r="E70" s="41"/>
-      <c r="F70" s="41"/>
-      <c r="G70" s="41"/>
-      <c r="H70" s="41"/>
-      <c r="I70" s="41"/>
-      <c r="J70" s="41"/>
-      <c r="K70" s="41"/>
-      <c r="L70" s="41"/>
-      <c r="M70" s="41"/>
+      <c r="A70" s="42"/>
+      <c r="B70" s="42"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="42"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
+      <c r="L70" s="42"/>
+      <c r="M70" s="42"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3773,7 +3788,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3785,7 +3800,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/预推免院校/汇总.xlsx
+++ b/预推免院校/汇总.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="185">
   <si>
     <t>序号</t>
   </si>
@@ -238,6 +238,9 @@
     <t>电子科技大学</t>
   </si>
   <si>
+    <t>智能计算研究院</t>
+  </si>
+  <si>
     <t>https://yzbm.uestc.edu.cn/logon</t>
   </si>
   <si>
@@ -533,6 +536,54 @@
   </si>
   <si>
     <t>西南交通大学</t>
+  </si>
+  <si>
+    <t>填写问卷</t>
+  </si>
+  <si>
+    <t>吉林大学</t>
+  </si>
+  <si>
+    <t>https://csw.jlu.edu.cn/info/1156/7969.htm</t>
+  </si>
+  <si>
+    <t>https://yzb.jlu.edu.cn/tmsbm/login</t>
+  </si>
+  <si>
+    <t>郑州大学</t>
+  </si>
+  <si>
+    <t>计算机与人工智能学院、软件学院</t>
+  </si>
+  <si>
+    <t>https://www7.zzu.edu.cn/csai/info/1147/3573.htm</t>
+  </si>
+  <si>
+    <t>上海大学</t>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/UUHT9naLSN-mbtOffA2h9A</t>
+  </si>
+  <si>
+    <t>上海大学研究生院</t>
+  </si>
+  <si>
+    <t>西北农林</t>
+  </si>
+  <si>
+    <t>https://yjszs.nwafu.edu.cn/yjszs/plugins/zs/zsxsd/entrance#/login</t>
+  </si>
+  <si>
+    <t>湖南师范大学</t>
+  </si>
+  <si>
+    <t>https://yjsy.hunnu.edu.cn/info/1027/15918.htm</t>
+  </si>
+  <si>
+    <t>武汉理工大学</t>
+  </si>
+  <si>
+    <t>http://whlg.form.360eol.com/enroll/325Jhlv4</t>
   </si>
 </sst>
 </file>
@@ -546,7 +597,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,13 +630,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -624,22 +675,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <u/>
       <sz val="11"/>
@@ -659,6 +694,22 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -676,14 +727,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1158,137 +1201,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1298,9 +1341,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1313,16 +1353,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1358,37 +1395,22 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1400,7 +1422,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1409,13 +1431,10 @@
     <xf numFmtId="58" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1424,70 +1443,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="6" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1807,1898 +1811,2000 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="17.7916666666667" customWidth="1"/>
-    <col min="3" max="3" width="31.0416666666667" customWidth="1"/>
+    <col min="2" max="2" width="17.7909090909091" customWidth="1"/>
+    <col min="3" max="3" width="31.0454545454545" customWidth="1"/>
     <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="5" max="5" width="51.8083333333333" customWidth="1"/>
-    <col min="6" max="6" width="17.4833333333333" customWidth="1"/>
-    <col min="7" max="7" width="16.7833333333333" customWidth="1"/>
-    <col min="8" max="8" width="14.125"/>
+    <col min="5" max="5" width="51.8090909090909" customWidth="1"/>
+    <col min="6" max="6" width="17.4818181818182" customWidth="1"/>
+    <col min="7" max="7" width="16.7818181818182" customWidth="1"/>
+    <col min="8" max="8" width="14.1272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:13">
-      <c r="A2" s="14">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="D2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="14">
         <v>45840</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="18">
+      <c r="H2" s="16">
         <v>20263300215</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="16" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="14"/>
+      <c r="M2" s="12"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:13">
-      <c r="A3" s="19">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="19">
         <v>45842</v>
       </c>
-      <c r="G3" s="21">
+      <c r="G3" s="19">
         <v>45900</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:13">
-      <c r="A4" s="14">
+      <c r="A4" s="12">
         <v>4</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="15" t="s">
+      <c r="D4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="14">
         <v>45848</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="14">
         <v>45918</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="14"/>
-    </row>
-    <row r="5" s="3" customFormat="1" spans="1:13">
-      <c r="A5" s="23">
+      <c r="M4" s="12"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:13">
+      <c r="A5" s="12">
         <v>5</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="64" t="s">
+      <c r="D5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="12"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:13">
-      <c r="A6" s="23">
+      <c r="A6" s="21">
         <v>6</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="25" t="s">
+      <c r="D6" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24" t="s">
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="64" t="s">
+      <c r="J6" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-    </row>
-    <row r="7" s="4" customFormat="1" spans="1:13">
-      <c r="A7" s="26">
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+    </row>
+    <row r="7" s="3" customFormat="1" spans="1:13">
+      <c r="A7" s="21">
         <v>7</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="27" t="s">
+      <c r="D7" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="24">
         <v>45874</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="24">
         <v>45897</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="23">
         <v>20263300074</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="27" t="s">
+      <c r="J7" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="K7" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-    </row>
-    <row r="8" s="4" customFormat="1" spans="1:13">
-      <c r="A8" s="26">
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="1:13">
+      <c r="A8" s="21">
         <v>8</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="27" t="s">
+      <c r="D8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="24">
         <v>45864</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="24">
         <v>45920</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="23">
         <v>26002158</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="27" t="s">
+      <c r="J8" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:13">
-      <c r="A9" s="23">
+      <c r="A9" s="21">
         <v>9</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="30" t="s">
+      <c r="D9" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="24">
         <v>45867</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="24">
         <v>45879</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="23">
         <v>20263308927</v>
       </c>
-      <c r="I9" s="24" t="s">
+      <c r="I9" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="65" t="s">
+      <c r="J9" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-    </row>
-    <row r="10" s="5" customFormat="1" spans="1:13">
-      <c r="A10" s="32">
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+    </row>
+    <row r="10" s="4" customFormat="1" spans="1:13">
+      <c r="A10" s="25">
         <v>10</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="33" t="s">
+      <c r="D10" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="27">
         <v>45857</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="27">
         <v>45901</v>
       </c>
-      <c r="H10" s="35" t="s">
+      <c r="H10" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="35" t="s">
+      <c r="I10" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="33" t="s">
+      <c r="J10" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-    </row>
-    <row r="11" s="6" customFormat="1" spans="1:13">
-      <c r="A11" s="36">
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+    </row>
+    <row r="11" s="5" customFormat="1" spans="1:13">
+      <c r="A11" s="29">
         <v>11</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="37" t="s">
+      <c r="D11" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38" t="s">
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="38" t="s">
+      <c r="I11" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="37" t="s">
+      <c r="J11" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="K11" s="36" t="s">
+      <c r="K11" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="36" t="s">
+      <c r="L11" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="36" t="s">
+      <c r="M11" s="29" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:13">
-      <c r="A12" s="19">
+      <c r="A12" s="17">
         <v>12</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="22" t="s">
+      <c r="D12" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-    </row>
-    <row r="13" s="7" customFormat="1" spans="1:13">
-      <c r="A13" s="40">
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+    </row>
+    <row r="13" s="5" customFormat="1" spans="1:13">
+      <c r="A13" s="29">
         <v>13</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41">
+      <c r="C13" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="29"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31">
         <v>20263301375</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="54" t="s">
-        <v>69</v>
-      </c>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
+      <c r="J13" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="42">
+      <c r="A14" s="33">
         <v>14</v>
       </c>
-      <c r="B14" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="42" t="s">
+      <c r="B14" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="25" t="s">
+      <c r="C14" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="43">
+      <c r="D14" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="35">
         <v>45871</v>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="35">
         <v>45919</v>
       </c>
-      <c r="H14" s="44">
+      <c r="H14" s="36">
         <v>20262200196</v>
       </c>
-      <c r="I14" s="44" t="s">
+      <c r="I14" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-    </row>
-    <row r="15" s="8" customFormat="1" spans="1:13">
-      <c r="A15" s="45">
-        <v>15</v>
-      </c>
-      <c r="B15" s="19" t="s">
+      <c r="J14" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:13">
+      <c r="A15" s="17">
+        <v>15</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="20" t="s">
+      <c r="C15" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="46">
+      <c r="D15" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="32">
         <v>45839</v>
       </c>
-      <c r="G15" s="46">
+      <c r="G15" s="32">
         <v>45910</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45"/>
+      <c r="J15" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="42">
+      <c r="A16" s="33">
         <v>16</v>
       </c>
-      <c r="B16" s="42" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="42" t="s">
+      <c r="B16" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="25" t="s">
+      <c r="C16" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="47">
+      <c r="D16" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="37">
         <v>45855</v>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="37">
         <v>45897</v>
       </c>
-      <c r="H16" s="42">
+      <c r="H16" s="33">
         <v>202601506</v>
       </c>
-      <c r="I16" s="42" t="s">
+      <c r="I16" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="K16" s="42"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="42"/>
-    </row>
-    <row r="17" s="4" customFormat="1" spans="1:13">
-      <c r="A17" s="26">
+      <c r="J16" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+    </row>
+    <row r="17" s="3" customFormat="1" spans="1:13">
+      <c r="A17" s="21">
         <v>17</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="B17" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F17" s="48">
+      <c r="D17" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="38">
         <v>45886</v>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="38">
         <v>45916</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="21">
         <v>20263312838</v>
       </c>
-      <c r="I17" s="26" t="s">
+      <c r="I17" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
-    </row>
-    <row r="18" s="9" customFormat="1" spans="1:13">
-      <c r="A18" s="49">
+      <c r="J17" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+    </row>
+    <row r="18" s="6" customFormat="1" spans="1:13">
+      <c r="A18" s="39">
         <v>18</v>
       </c>
-      <c r="B18" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" s="49" t="s">
+      <c r="B18" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49" t="s">
+      <c r="D18" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="I18" s="49" t="s">
+      <c r="I18" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="K18" s="49"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="49"/>
+      <c r="J18" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="42">
+      <c r="A19" s="33">
         <v>19</v>
       </c>
-      <c r="B19" s="42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="42" t="s">
+      <c r="B19" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="51" t="s">
+      <c r="C19" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="47">
+      <c r="D19" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="37">
         <v>45901</v>
       </c>
-      <c r="G19" s="47">
+      <c r="G19" s="37">
         <v>45915</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="I19" s="42" t="s">
+      <c r="I19" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:13">
+      <c r="A20" s="12">
+        <v>20</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+    </row>
+    <row r="21" s="6" customFormat="1" spans="1:13">
+      <c r="A21" s="39">
+        <v>21</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="42">
+        <v>45903</v>
+      </c>
+      <c r="G21" s="42">
+        <v>45912</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="J21" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="1:13">
+      <c r="A22" s="21">
+        <v>19</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-    </row>
-    <row r="20" s="10" customFormat="1" spans="1:13">
-      <c r="A20" s="52">
+      <c r="F22" s="38">
+        <v>45901</v>
+      </c>
+      <c r="G22" s="38">
+        <v>45915</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="33">
+        <v>19</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="37">
+        <v>45901</v>
+      </c>
+      <c r="G23" s="37">
+        <v>45915</v>
+      </c>
+      <c r="H23" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="33">
+        <v>24</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="37">
+        <v>45871</v>
+      </c>
+      <c r="G24" s="37">
+        <v>45903</v>
+      </c>
+      <c r="H24" s="33">
+        <v>20253305016</v>
+      </c>
+      <c r="I24" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+    </row>
+    <row r="25" s="7" customFormat="1" spans="1:13">
+      <c r="A25" s="43">
+        <v>25</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" s="45">
+        <v>45894</v>
+      </c>
+      <c r="G25" s="45">
+        <v>45912</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+    </row>
+    <row r="26" s="5" customFormat="1" spans="1:13">
+      <c r="A26" s="29">
+        <v>26</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="46">
+        <v>45890</v>
+      </c>
+      <c r="G26" s="46">
+        <v>45919</v>
+      </c>
+      <c r="H26" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:13">
+      <c r="A27" s="12">
+        <v>27</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="47">
+        <v>45902</v>
+      </c>
+      <c r="G27" s="47">
+        <v>45915</v>
+      </c>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+    </row>
+    <row r="28" s="5" customFormat="1" spans="1:13">
+      <c r="A28" s="29">
+        <v>28</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:13">
+      <c r="A29" s="12">
+        <v>29</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="F29" s="47">
+        <v>45902</v>
+      </c>
+      <c r="G29" s="47">
+        <v>45915</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="K29" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="14" t="s">
+      <c r="L29" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" s="12"/>
+    </row>
+    <row r="30" s="3" customFormat="1" spans="1:13">
+      <c r="A30" s="21">
+        <v>30</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" s="38">
+        <v>45902</v>
+      </c>
+      <c r="G30" s="38">
+        <v>45910</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I30" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+    </row>
+    <row r="31" s="3" customFormat="1" spans="1:13">
+      <c r="A31" s="21">
+        <v>31</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" s="38">
+        <v>45906</v>
+      </c>
+      <c r="G31" s="38">
+        <v>45910</v>
+      </c>
+      <c r="H31" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I31" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="K20" s="52"/>
-      <c r="L20" s="52"/>
-      <c r="M20" s="52"/>
-    </row>
-    <row r="21" s="9" customFormat="1" spans="1:13">
-      <c r="A21" s="49">
-        <v>21</v>
-      </c>
-      <c r="B21" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="49" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="F21" s="53">
+      <c r="J31" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" s="6" customFormat="1" spans="1:13">
+      <c r="A32" s="39">
+        <v>32</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32" s="42">
         <v>45903</v>
       </c>
-      <c r="G21" s="53">
+      <c r="G32" s="42">
+        <v>45915</v>
+      </c>
+      <c r="H32" s="39">
+        <v>20263304452</v>
+      </c>
+      <c r="I32" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="K32" s="39"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="39"/>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:13">
+      <c r="A33" s="12">
+        <v>33</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="F33" s="47">
+        <v>45905</v>
+      </c>
+      <c r="G33" s="47">
+        <v>45909</v>
+      </c>
+      <c r="H33" s="12">
+        <v>20263311417</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M33" s="12"/>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="33">
+        <v>34</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" s="33"/>
+      <c r="E34" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="F34" s="37">
+        <v>45880</v>
+      </c>
+      <c r="G34" s="37">
+        <v>45910</v>
+      </c>
+      <c r="H34" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="I34" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:13">
+      <c r="A35" s="12">
+        <v>35</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12">
+        <v>202608849</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K35" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="M35" s="12"/>
+    </row>
+    <row r="36" s="3" customFormat="1" spans="1:13">
+      <c r="A36" s="21">
+        <v>36</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F36" s="38">
+        <v>45904</v>
+      </c>
+      <c r="G36" s="38">
         <v>45912</v>
       </c>
-      <c r="H21" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="I21" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="J21" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="K21" s="49"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="42">
-        <v>19</v>
-      </c>
-      <c r="B22" s="42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" s="47">
-        <v>45901</v>
-      </c>
-      <c r="G22" s="47">
+      <c r="H36" s="21">
+        <v>20263327091</v>
+      </c>
+      <c r="I36" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="21"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:13">
+      <c r="A37" s="12">
+        <v>37</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+    </row>
+    <row r="38" s="5" customFormat="1" spans="1:13">
+      <c r="A38" s="29">
+        <v>38</v>
+      </c>
+      <c r="B38" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="F38" s="46">
+        <v>45904</v>
+      </c>
+      <c r="G38" s="46">
+        <v>45913</v>
+      </c>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="33">
+        <v>39</v>
+      </c>
+      <c r="B39" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="E39" s="44" t="s">
+        <v>153</v>
+      </c>
+      <c r="F39" s="45">
+        <v>45909</v>
+      </c>
+      <c r="G39" s="45">
         <v>45915</v>
       </c>
-      <c r="H22" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="I22" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="42">
-        <v>19</v>
-      </c>
-      <c r="B23" s="42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="F23" s="47">
-        <v>45901</v>
-      </c>
-      <c r="G23" s="47">
-        <v>45915</v>
-      </c>
-      <c r="H23" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="I23" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="42"/>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="42">
-        <v>24</v>
-      </c>
-      <c r="B24" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24" s="47">
-        <v>45871</v>
-      </c>
-      <c r="G24" s="47">
-        <v>45903</v>
-      </c>
-      <c r="H24" s="42">
-        <v>20253305016</v>
-      </c>
-      <c r="I24" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="K24" s="42"/>
-      <c r="L24" s="42"/>
-      <c r="M24" s="42"/>
-    </row>
-    <row r="25" s="7" customFormat="1" spans="1:13">
-      <c r="A25" s="40">
-        <v>25</v>
-      </c>
-      <c r="B25" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="54" t="s">
-        <v>106</v>
-      </c>
-      <c r="F25" s="55">
-        <v>45894</v>
-      </c>
-      <c r="G25" s="55">
-        <v>45912</v>
-      </c>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="40"/>
-    </row>
-    <row r="26" s="9" customFormat="1" spans="1:13">
-      <c r="A26" s="49">
-        <v>26</v>
-      </c>
-      <c r="B26" s="49" t="s">
-        <v>107</v>
-      </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="F26" s="53">
-        <v>45890</v>
-      </c>
-      <c r="G26" s="53">
-        <v>45919</v>
-      </c>
-      <c r="H26" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="I26" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-    </row>
-    <row r="27" s="10" customFormat="1" spans="1:13">
-      <c r="A27" s="52">
-        <v>27</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="F27" s="56">
-        <v>45902</v>
-      </c>
-      <c r="G27" s="56">
-        <v>45915</v>
-      </c>
-      <c r="H27" s="52"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="K27" s="52"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="52"/>
-    </row>
-    <row r="28" s="6" customFormat="1" spans="1:13">
-      <c r="A28" s="36">
-        <v>28</v>
-      </c>
-      <c r="B28" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="I28" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="K28" s="36"/>
-      <c r="L28" s="36"/>
-      <c r="M28" s="36"/>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:13">
-      <c r="A29" s="14">
-        <v>29</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="F29" s="58">
-        <v>45902</v>
-      </c>
-      <c r="G29" s="58">
-        <v>45915</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="I29" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L29" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="M29" s="14"/>
-    </row>
-    <row r="30" s="11" customFormat="1" spans="1:13">
-      <c r="A30" s="59">
-        <v>30</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="F30" s="60">
-        <v>45902</v>
-      </c>
-      <c r="G30" s="60">
-        <v>45910</v>
-      </c>
-      <c r="H30" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="I30" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J30" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="K30" s="59"/>
-      <c r="L30" s="59"/>
-      <c r="M30" s="59"/>
-    </row>
-    <row r="31" s="4" customFormat="1" spans="1:13">
-      <c r="A31" s="26">
-        <v>31</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="C31" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="48">
-        <v>45906</v>
-      </c>
-      <c r="G31" s="48">
-        <v>45910</v>
-      </c>
-      <c r="H31" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="I31" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J31" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" s="7" customFormat="1" spans="1:13">
-      <c r="A32" s="40">
-        <v>32</v>
-      </c>
-      <c r="B32" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="E32" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="F32" s="55">
-        <v>45903</v>
-      </c>
-      <c r="G32" s="55">
-        <v>45915</v>
-      </c>
-      <c r="H32" s="40">
-        <v>20263304452</v>
-      </c>
-      <c r="I32" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="K32" s="40"/>
-      <c r="L32" s="40"/>
-      <c r="M32" s="40"/>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:13">
-      <c r="A33" s="14">
-        <v>33</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="F33" s="58">
-        <v>45905</v>
-      </c>
-      <c r="G33" s="58">
-        <v>45909</v>
-      </c>
-      <c r="H33" s="14">
-        <v>20263311417</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J33" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="K33" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L33" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="M33" s="14"/>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="42">
-        <v>34</v>
-      </c>
-      <c r="B34" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>133</v>
-      </c>
-      <c r="D34" s="42"/>
-      <c r="E34" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="F34" s="47">
-        <v>45880</v>
-      </c>
-      <c r="G34" s="47">
-        <v>45910</v>
-      </c>
-      <c r="H34" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="I34" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="J34" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="K34" s="42"/>
-      <c r="L34" s="42"/>
-      <c r="M34" s="42"/>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:13">
-      <c r="A35" s="14">
-        <v>35</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14">
-        <v>202608849</v>
-      </c>
-      <c r="I35" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L35" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="M35" s="14"/>
-    </row>
-    <row r="36" s="11" customFormat="1" spans="1:13">
-      <c r="A36" s="59">
-        <v>36</v>
-      </c>
-      <c r="B36" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="C36" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F36" s="60">
-        <v>45904</v>
-      </c>
-      <c r="G36" s="60">
-        <v>45912</v>
-      </c>
-      <c r="H36" s="59">
-        <v>20263327091</v>
-      </c>
-      <c r="I36" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="K36" s="59"/>
-      <c r="L36" s="59"/>
-      <c r="M36" s="59"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:13">
-      <c r="A37" s="14">
-        <v>37</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-    </row>
-    <row r="38" s="6" customFormat="1" spans="1:15">
-      <c r="A38" s="62">
-        <v>38</v>
-      </c>
-      <c r="B38" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="C38" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="D38" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="F38" s="63">
-        <v>45904</v>
-      </c>
-      <c r="G38" s="63">
-        <v>45913</v>
-      </c>
-      <c r="H38" s="62"/>
-      <c r="I38" s="62"/>
-      <c r="J38" s="62"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="62"/>
-      <c r="M38" s="62"/>
-      <c r="N38" s="66"/>
-      <c r="O38" s="66"/>
-    </row>
-    <row r="39" spans="1:15">
-      <c r="A39" s="42">
-        <v>39</v>
-      </c>
-      <c r="B39" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="C39" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="E39" s="54" t="s">
-        <v>152</v>
-      </c>
-      <c r="F39" s="55">
-        <v>45909</v>
-      </c>
-      <c r="G39" s="55">
-        <v>45915</v>
-      </c>
-      <c r="H39" s="40">
+      <c r="H39" s="43">
         <v>202602944</v>
       </c>
-      <c r="I39" s="54" t="s">
-        <v>153</v>
-      </c>
-      <c r="J39" s="40"/>
-      <c r="K39" s="40"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="40"/>
+      <c r="I39" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="43"/>
       <c r="N39" s="7"/>
       <c r="O39" s="7"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:13">
-      <c r="A40" s="14">
+      <c r="A40" s="12">
         <v>40</v>
       </c>
-      <c r="B40" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="C40" s="14" t="s">
+      <c r="B40" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="F40" s="58">
+      <c r="D40" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="47">
         <v>45908</v>
       </c>
-      <c r="G40" s="58">
+      <c r="G40" s="47">
         <v>45921</v>
       </c>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
     </row>
     <row r="41" s="7" customFormat="1" spans="1:15">
-      <c r="A41" s="42">
+      <c r="A41" s="33">
         <v>41</v>
       </c>
-      <c r="B41" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="C41" s="42" t="s">
+      <c r="B41" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="D41" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="51" t="s">
+      <c r="C41" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="F41" s="47">
+      <c r="D41" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="F41" s="37">
         <v>45910</v>
       </c>
-      <c r="G41" s="47">
+      <c r="G41" s="37">
         <v>45916</v>
       </c>
-      <c r="H41" s="42" t="s">
+      <c r="H41" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="42" t="s">
+      <c r="I41" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="J41" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="K41" s="42"/>
-      <c r="L41" s="42"/>
-      <c r="M41" s="42"/>
+      <c r="J41" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="K41" s="33"/>
+      <c r="L41" s="33"/>
+      <c r="M41" s="33"/>
       <c r="N41"/>
       <c r="O41"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="42">
+      <c r="A42" s="33">
         <v>42</v>
       </c>
-      <c r="B42" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="C42" s="42" t="s">
+      <c r="B42" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="D42" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" s="51" t="s">
+      <c r="C42" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F42" s="47">
+      <c r="D42" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="F42" s="37">
         <v>45909</v>
       </c>
-      <c r="G42" s="47">
+      <c r="G42" s="37">
         <v>45922</v>
       </c>
-      <c r="H42" s="42">
+      <c r="H42" s="33">
         <v>202601040</v>
       </c>
-      <c r="I42" s="42" t="s">
+      <c r="I42" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="J42" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
+      <c r="J42" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="33"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:13">
-      <c r="A43" s="14">
+      <c r="A43" s="12">
         <v>43</v>
       </c>
-      <c r="B43" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C43" s="14" t="s">
+      <c r="B43" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C43" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14">
+      <c r="D43" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12">
         <v>20263309395</v>
       </c>
-      <c r="I43" s="14" t="s">
+      <c r="I43" s="12" t="s">
         <v>18</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="14"/>
+        <v>167</v>
+      </c>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="12"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="42">
+      <c r="A44" s="33">
         <v>44</v>
       </c>
-      <c r="B44" s="42" t="s">
-        <v>167</v>
-      </c>
-      <c r="C44" s="42" t="s">
-        <v>93</v>
-      </c>
-      <c r="D44" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="42"/>
-      <c r="H44" s="42"/>
-      <c r="I44" s="42"/>
-      <c r="J44" s="42"/>
-      <c r="K44" s="42"/>
-      <c r="L44" s="42"/>
-      <c r="M44" s="42"/>
-    </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="42">
+      <c r="B44" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="33"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="33"/>
+      <c r="M44" s="33" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" s="8" customFormat="1" spans="1:13">
+      <c r="A45" s="50">
         <v>45</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="42"/>
-      <c r="I45" s="42"/>
-      <c r="J45" s="42"/>
-      <c r="K45" s="42"/>
-      <c r="L45" s="42"/>
-      <c r="M45" s="42"/>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="42">
+      <c r="B45" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="F45" s="51">
+        <v>45912</v>
+      </c>
+      <c r="G45" s="51">
+        <v>45915</v>
+      </c>
+      <c r="H45" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="I45" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="K45" s="50"/>
+      <c r="L45" s="50"/>
+      <c r="M45" s="50"/>
+    </row>
+    <row r="46" s="6" customFormat="1" spans="1:13">
+      <c r="A46" s="39">
         <v>46</v>
       </c>
-      <c r="B46" s="42"/>
-      <c r="C46" s="42"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="42"/>
-      <c r="H46" s="42"/>
-      <c r="I46" s="42"/>
-      <c r="J46" s="42"/>
-      <c r="K46" s="42"/>
-      <c r="L46" s="42"/>
-      <c r="M46" s="42"/>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="42">
+      <c r="B46" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="C46" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="D46" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="F46" s="42">
+        <v>45915</v>
+      </c>
+      <c r="G46" s="42">
+        <v>45920</v>
+      </c>
+      <c r="H46" s="39"/>
+      <c r="I46" s="39"/>
+      <c r="J46" s="39"/>
+      <c r="K46" s="39"/>
+      <c r="L46" s="39"/>
+      <c r="M46" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="47" s="9" customFormat="1" spans="1:13">
+      <c r="A47" s="52">
         <v>47</v>
       </c>
-      <c r="B47" s="42"/>
-      <c r="C47" s="42"/>
-      <c r="D47" s="42"/>
-      <c r="E47" s="42"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="42"/>
-      <c r="H47" s="42"/>
-      <c r="I47" s="42"/>
-      <c r="J47" s="42"/>
-      <c r="K47" s="42"/>
-      <c r="L47" s="42"/>
-      <c r="M47" s="42"/>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="A48" s="42">
+      <c r="B47" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="52"/>
+      <c r="L47" s="52"/>
+      <c r="M47" s="12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="1:13">
+      <c r="A48" s="12">
         <v>48</v>
       </c>
-      <c r="B48" s="42"/>
-      <c r="C48" s="42"/>
-      <c r="D48" s="42"/>
-      <c r="E48" s="42"/>
-      <c r="F48" s="42"/>
-      <c r="G48" s="42"/>
-      <c r="H48" s="42"/>
-      <c r="I48" s="42"/>
-      <c r="J48" s="42"/>
-      <c r="K48" s="42"/>
-      <c r="L48" s="42"/>
-      <c r="M48" s="42"/>
+      <c r="B48" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="42">
+      <c r="A49" s="33">
         <v>49</v>
       </c>
-      <c r="B49" s="42"/>
-      <c r="C49" s="42"/>
-      <c r="D49" s="42"/>
-      <c r="E49" s="42"/>
-      <c r="F49" s="42"/>
-      <c r="G49" s="42"/>
-      <c r="H49" s="42"/>
-      <c r="I49" s="42"/>
-      <c r="J49" s="42"/>
-      <c r="K49" s="42"/>
-      <c r="L49" s="42"/>
-      <c r="M49" s="42"/>
+      <c r="B49" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="C49" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="33"/>
+      <c r="F49" s="33"/>
+      <c r="G49" s="33"/>
+      <c r="H49" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="K49" s="33"/>
+      <c r="L49" s="33"/>
+      <c r="M49" s="33"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="42"/>
-      <c r="B50" s="42"/>
-      <c r="C50" s="42"/>
-      <c r="D50" s="42"/>
-      <c r="E50" s="42"/>
-      <c r="F50" s="42"/>
-      <c r="G50" s="42"/>
-      <c r="H50" s="42"/>
-      <c r="I50" s="42"/>
-      <c r="J50" s="42"/>
-      <c r="K50" s="42"/>
-      <c r="L50" s="42"/>
-      <c r="M50" s="42"/>
+      <c r="A50" s="33">
+        <v>50</v>
+      </c>
+      <c r="B50" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="C50" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="F50" s="37">
+        <v>45904</v>
+      </c>
+      <c r="G50" s="37">
+        <v>45915</v>
+      </c>
+      <c r="H50" s="33">
+        <v>2513269</v>
+      </c>
+      <c r="I50" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="33"/>
+      <c r="K50" s="33"/>
+      <c r="L50" s="33"/>
+      <c r="M50" s="33"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="42"/>
-      <c r="B51" s="42"/>
-      <c r="C51" s="42"/>
-      <c r="D51" s="42"/>
-      <c r="E51" s="42"/>
-      <c r="F51" s="42"/>
-      <c r="G51" s="42"/>
-      <c r="H51" s="42"/>
-      <c r="I51" s="42"/>
-      <c r="J51" s="42"/>
-      <c r="K51" s="42"/>
-      <c r="L51" s="42"/>
-      <c r="M51" s="42"/>
+      <c r="A51" s="33">
+        <v>51</v>
+      </c>
+      <c r="B51" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="33"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="33"/>
+      <c r="H51" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="K51" s="33"/>
+      <c r="L51" s="33"/>
+      <c r="M51" s="33"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="42"/>
-      <c r="B52" s="42"/>
-      <c r="C52" s="42"/>
-      <c r="D52" s="42"/>
-      <c r="E52" s="42"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="42"/>
-      <c r="H52" s="42"/>
-      <c r="I52" s="42"/>
-      <c r="J52" s="42"/>
-      <c r="K52" s="42"/>
-      <c r="L52" s="42"/>
-      <c r="M52" s="42"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="33"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="33"/>
+      <c r="G52" s="33"/>
+      <c r="H52" s="33"/>
+      <c r="I52" s="33"/>
+      <c r="J52" s="33"/>
+      <c r="K52" s="33"/>
+      <c r="L52" s="33"/>
+      <c r="M52" s="33"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="42"/>
-      <c r="B53" s="42"/>
-      <c r="C53" s="42"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="42"/>
-      <c r="F53" s="42"/>
-      <c r="G53" s="42"/>
-      <c r="H53" s="42"/>
-      <c r="I53" s="42"/>
-      <c r="J53" s="42"/>
-      <c r="K53" s="42"/>
-      <c r="L53" s="42"/>
-      <c r="M53" s="42"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="33"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="33"/>
+      <c r="H53" s="33"/>
+      <c r="I53" s="33"/>
+      <c r="J53" s="33"/>
+      <c r="K53" s="33"/>
+      <c r="L53" s="33"/>
+      <c r="M53" s="33"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="42"/>
-      <c r="B54" s="42"/>
-      <c r="C54" s="42"/>
-      <c r="D54" s="42"/>
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="42"/>
-      <c r="H54" s="42"/>
-      <c r="I54" s="42"/>
-      <c r="J54" s="42"/>
-      <c r="K54" s="42"/>
-      <c r="L54" s="42"/>
-      <c r="M54" s="42"/>
+      <c r="A54" s="33"/>
+      <c r="B54" s="33"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="33"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="33"/>
+      <c r="H54" s="33"/>
+      <c r="I54" s="33"/>
+      <c r="J54" s="33"/>
+      <c r="K54" s="33"/>
+      <c r="L54" s="33"/>
+      <c r="M54" s="33"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="42"/>
-      <c r="B55" s="42"/>
-      <c r="C55" s="42"/>
-      <c r="D55" s="42"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="42"/>
-      <c r="H55" s="42"/>
-      <c r="I55" s="42"/>
-      <c r="J55" s="42"/>
-      <c r="K55" s="42"/>
-      <c r="L55" s="42"/>
-      <c r="M55" s="42"/>
+      <c r="A55" s="33"/>
+      <c r="B55" s="33"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="33"/>
+      <c r="E55" s="33"/>
+      <c r="F55" s="33"/>
+      <c r="G55" s="33"/>
+      <c r="H55" s="33"/>
+      <c r="I55" s="33"/>
+      <c r="J55" s="33"/>
+      <c r="K55" s="33"/>
+      <c r="L55" s="33"/>
+      <c r="M55" s="33"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="42"/>
-      <c r="B56" s="42"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="42"/>
-      <c r="E56" s="42"/>
-      <c r="F56" s="42"/>
-      <c r="G56" s="42"/>
-      <c r="H56" s="42"/>
-      <c r="I56" s="42"/>
-      <c r="J56" s="42"/>
-      <c r="K56" s="42"/>
-      <c r="L56" s="42"/>
-      <c r="M56" s="42"/>
+      <c r="A56" s="33"/>
+      <c r="B56" s="33"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="33"/>
+      <c r="I56" s="33"/>
+      <c r="J56" s="33"/>
+      <c r="K56" s="33"/>
+      <c r="L56" s="33"/>
+      <c r="M56" s="33"/>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="42"/>
-      <c r="B57" s="42"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="42"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="42"/>
-      <c r="I57" s="42"/>
-      <c r="J57" s="42"/>
-      <c r="K57" s="42"/>
-      <c r="L57" s="42"/>
-      <c r="M57" s="42"/>
+      <c r="A57" s="33"/>
+      <c r="B57" s="33"/>
+      <c r="C57" s="33"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="33"/>
+      <c r="F57" s="33"/>
+      <c r="G57" s="33"/>
+      <c r="H57" s="33"/>
+      <c r="I57" s="33"/>
+      <c r="J57" s="33"/>
+      <c r="K57" s="33"/>
+      <c r="L57" s="33"/>
+      <c r="M57" s="33"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="42"/>
-      <c r="B58" s="42"/>
-      <c r="C58" s="42"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="42"/>
-      <c r="H58" s="42"/>
-      <c r="I58" s="42"/>
-      <c r="J58" s="42"/>
-      <c r="K58" s="42"/>
-      <c r="L58" s="42"/>
-      <c r="M58" s="42"/>
+      <c r="A58" s="33"/>
+      <c r="B58" s="33"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="33"/>
+      <c r="E58" s="33"/>
+      <c r="F58" s="33"/>
+      <c r="G58" s="33"/>
+      <c r="H58" s="33"/>
+      <c r="I58" s="33"/>
+      <c r="J58" s="33"/>
+      <c r="K58" s="33"/>
+      <c r="L58" s="33"/>
+      <c r="M58" s="33"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="42"/>
-      <c r="B59" s="42"/>
-      <c r="C59" s="42"/>
-      <c r="D59" s="42"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="42"/>
-      <c r="H59" s="42"/>
-      <c r="I59" s="42"/>
-      <c r="J59" s="42"/>
-      <c r="K59" s="42"/>
-      <c r="L59" s="42"/>
-      <c r="M59" s="42"/>
+      <c r="A59" s="33"/>
+      <c r="B59" s="33"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="33"/>
+      <c r="J59" s="33"/>
+      <c r="K59" s="33"/>
+      <c r="L59" s="33"/>
+      <c r="M59" s="33"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="42"/>
-      <c r="B60" s="42"/>
-      <c r="C60" s="42"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="42"/>
-      <c r="H60" s="42"/>
-      <c r="I60" s="42"/>
-      <c r="J60" s="42"/>
-      <c r="K60" s="42"/>
-      <c r="L60" s="42"/>
-      <c r="M60" s="42"/>
+      <c r="A60" s="33"/>
+      <c r="B60" s="33"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="33"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="33"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="33"/>
+      <c r="M60" s="33"/>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="42"/>
-      <c r="B61" s="42"/>
-      <c r="C61" s="42"/>
-      <c r="D61" s="42"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="42"/>
-      <c r="H61" s="42"/>
-      <c r="I61" s="42"/>
-      <c r="J61" s="42"/>
-      <c r="K61" s="42"/>
-      <c r="L61" s="42"/>
-      <c r="M61" s="42"/>
+      <c r="A61" s="33"/>
+      <c r="B61" s="33"/>
+      <c r="C61" s="33"/>
+      <c r="D61" s="33"/>
+      <c r="E61" s="33"/>
+      <c r="F61" s="33"/>
+      <c r="G61" s="33"/>
+      <c r="H61" s="33"/>
+      <c r="I61" s="33"/>
+      <c r="J61" s="33"/>
+      <c r="K61" s="33"/>
+      <c r="L61" s="33"/>
+      <c r="M61" s="33"/>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="42"/>
-      <c r="B62" s="42"/>
-      <c r="C62" s="42"/>
-      <c r="D62" s="42"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="42"/>
-      <c r="G62" s="42"/>
-      <c r="H62" s="42"/>
-      <c r="I62" s="42"/>
-      <c r="J62" s="42"/>
-      <c r="K62" s="42"/>
-      <c r="L62" s="42"/>
-      <c r="M62" s="42"/>
+      <c r="A62" s="33"/>
+      <c r="B62" s="33"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="33"/>
+      <c r="E62" s="33"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="33"/>
+      <c r="H62" s="33"/>
+      <c r="I62" s="33"/>
+      <c r="J62" s="33"/>
+      <c r="K62" s="33"/>
+      <c r="L62" s="33"/>
+      <c r="M62" s="33"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="42"/>
-      <c r="B63" s="42"/>
-      <c r="C63" s="42"/>
-      <c r="D63" s="42"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="42"/>
-      <c r="G63" s="42"/>
-      <c r="H63" s="42"/>
-      <c r="I63" s="42"/>
-      <c r="J63" s="42"/>
-      <c r="K63" s="42"/>
-      <c r="L63" s="42"/>
-      <c r="M63" s="42"/>
+      <c r="A63" s="33"/>
+      <c r="B63" s="33"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+      <c r="M63" s="33"/>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="42"/>
-      <c r="B64" s="42"/>
-      <c r="C64" s="42"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="42"/>
-      <c r="G64" s="42"/>
-      <c r="H64" s="42"/>
-      <c r="I64" s="42"/>
-      <c r="J64" s="42"/>
-      <c r="K64" s="42"/>
-      <c r="L64" s="42"/>
-      <c r="M64" s="42"/>
+      <c r="A64" s="33"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="33"/>
+      <c r="E64" s="33"/>
+      <c r="F64" s="33"/>
+      <c r="G64" s="33"/>
+      <c r="H64" s="33"/>
+      <c r="I64" s="33"/>
+      <c r="J64" s="33"/>
+      <c r="K64" s="33"/>
+      <c r="L64" s="33"/>
+      <c r="M64" s="33"/>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="42"/>
-      <c r="B65" s="42"/>
-      <c r="C65" s="42"/>
-      <c r="D65" s="42"/>
-      <c r="E65" s="42"/>
-      <c r="F65" s="42"/>
-      <c r="G65" s="42"/>
-      <c r="H65" s="42"/>
-      <c r="I65" s="42"/>
-      <c r="J65" s="42"/>
-      <c r="K65" s="42"/>
-      <c r="L65" s="42"/>
-      <c r="M65" s="42"/>
+      <c r="A65" s="33"/>
+      <c r="B65" s="33"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="33"/>
+      <c r="E65" s="33"/>
+      <c r="F65" s="33"/>
+      <c r="G65" s="33"/>
+      <c r="H65" s="33"/>
+      <c r="I65" s="33"/>
+      <c r="J65" s="33"/>
+      <c r="K65" s="33"/>
+      <c r="L65" s="33"/>
+      <c r="M65" s="33"/>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="42"/>
-      <c r="B66" s="42"/>
-      <c r="C66" s="42"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="42"/>
-      <c r="F66" s="42"/>
-      <c r="G66" s="42"/>
-      <c r="H66" s="42"/>
-      <c r="I66" s="42"/>
-      <c r="J66" s="42"/>
-      <c r="K66" s="42"/>
-      <c r="L66" s="42"/>
-      <c r="M66" s="42"/>
+      <c r="A66" s="33"/>
+      <c r="B66" s="33"/>
+      <c r="C66" s="33"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="33"/>
+      <c r="G66" s="33"/>
+      <c r="H66" s="33"/>
+      <c r="I66" s="33"/>
+      <c r="J66" s="33"/>
+      <c r="K66" s="33"/>
+      <c r="L66" s="33"/>
+      <c r="M66" s="33"/>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="42"/>
-      <c r="B67" s="42"/>
-      <c r="C67" s="42"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="42"/>
-      <c r="F67" s="42"/>
-      <c r="G67" s="42"/>
-      <c r="H67" s="42"/>
-      <c r="I67" s="42"/>
-      <c r="J67" s="42"/>
-      <c r="K67" s="42"/>
-      <c r="L67" s="42"/>
-      <c r="M67" s="42"/>
+      <c r="A67" s="33"/>
+      <c r="B67" s="33"/>
+      <c r="C67" s="33"/>
+      <c r="D67" s="33"/>
+      <c r="E67" s="33"/>
+      <c r="F67" s="33"/>
+      <c r="G67" s="33"/>
+      <c r="H67" s="33"/>
+      <c r="I67" s="33"/>
+      <c r="J67" s="33"/>
+      <c r="K67" s="33"/>
+      <c r="L67" s="33"/>
+      <c r="M67" s="33"/>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="42"/>
-      <c r="B68" s="42"/>
-      <c r="C68" s="42"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="42"/>
-      <c r="G68" s="42"/>
-      <c r="H68" s="42"/>
-      <c r="I68" s="42"/>
-      <c r="J68" s="42"/>
-      <c r="K68" s="42"/>
-      <c r="L68" s="42"/>
-      <c r="M68" s="42"/>
+      <c r="A68" s="33"/>
+      <c r="B68" s="33"/>
+      <c r="C68" s="33"/>
+      <c r="D68" s="33"/>
+      <c r="E68" s="33"/>
+      <c r="F68" s="33"/>
+      <c r="G68" s="33"/>
+      <c r="H68" s="33"/>
+      <c r="I68" s="33"/>
+      <c r="J68" s="33"/>
+      <c r="K68" s="33"/>
+      <c r="L68" s="33"/>
+      <c r="M68" s="33"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="42"/>
-      <c r="B69" s="42"/>
-      <c r="C69" s="42"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="G69" s="42"/>
-      <c r="H69" s="42"/>
-      <c r="I69" s="42"/>
-      <c r="J69" s="42"/>
-      <c r="K69" s="42"/>
-      <c r="L69" s="42"/>
-      <c r="M69" s="42"/>
+      <c r="A69" s="33"/>
+      <c r="B69" s="33"/>
+      <c r="C69" s="33"/>
+      <c r="D69" s="33"/>
+      <c r="E69" s="33"/>
+      <c r="F69" s="33"/>
+      <c r="G69" s="33"/>
+      <c r="H69" s="33"/>
+      <c r="I69" s="33"/>
+      <c r="J69" s="33"/>
+      <c r="K69" s="33"/>
+      <c r="L69" s="33"/>
+      <c r="M69" s="33"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="42"/>
-      <c r="B70" s="42"/>
-      <c r="C70" s="42"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="42"/>
-      <c r="G70" s="42"/>
-      <c r="H70" s="42"/>
-      <c r="I70" s="42"/>
-      <c r="J70" s="42"/>
-      <c r="K70" s="42"/>
-      <c r="L70" s="42"/>
-      <c r="M70" s="42"/>
+      <c r="A70" s="33"/>
+      <c r="B70" s="33"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="33"/>
+      <c r="E70" s="33"/>
+      <c r="F70" s="33"/>
+      <c r="G70" s="33"/>
+      <c r="H70" s="33"/>
+      <c r="I70" s="33"/>
+      <c r="J70" s="33"/>
+      <c r="K70" s="33"/>
+      <c r="L70" s="33"/>
+      <c r="M70" s="33"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3777,6 +3883,14 @@
     <hyperlink ref="E42" r:id="rId69" display="https://yz.jiangnan.edu.cn/info/1012/3674.htm"/>
     <hyperlink ref="J43" r:id="rId70" display="东华大学研究生报考服务系统" tooltip="https://yzbm.dhu.edu.cn/logon"/>
     <hyperlink ref="J27" r:id="rId71" display="http://swu.yjszsw.cn/tm/"/>
+    <hyperlink ref="J45" r:id="rId72" display="https://yzb.jlu.edu.cn/tmsbm/login"/>
+    <hyperlink ref="E45" r:id="rId73" display="https://csw.jlu.edu.cn/info/1156/7969.htm"/>
+    <hyperlink ref="E46" r:id="rId74" display="https://www7.zzu.edu.cn/csai/info/1147/3573.htm"/>
+    <hyperlink ref="E48" r:id="rId75" display="https://mp.weixin.qq.com/s/UUHT9naLSN-mbtOffA2h9A"/>
+    <hyperlink ref="J48" r:id="rId76" display="上海大学研究生院" tooltip="https://gmis.shu.edu.cn/php/bm/"/>
+    <hyperlink ref="J49" r:id="rId77" display="https://yjszs.nwafu.edu.cn/yjszs/plugins/zs/zsxsd/entrance#/login"/>
+    <hyperlink ref="E50" r:id="rId78" display="https://yjsy.hunnu.edu.cn/info/1027/15918.htm"/>
+    <hyperlink ref="J51" r:id="rId79" display="http://whlg.form.360eol.com/enroll/325Jhlv4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3788,7 +3902,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3800,7 +3914,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/预推免院校/汇总.xlsx
+++ b/预推免院校/汇总.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1331,7 +1331,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1350,16 +1350,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1398,12 +1395,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="58" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1431,18 +1428,21 @@
     <xf numFmtId="58" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1455,40 +1455,34 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="58" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="58" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1">
@@ -1811,552 +1805,552 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="17.7909090909091" customWidth="1"/>
-    <col min="3" max="3" width="31.0454545454545" customWidth="1"/>
+    <col min="2" max="2" width="17.7916666666667" customWidth="1"/>
+    <col min="3" max="3" width="31.0416666666667" customWidth="1"/>
     <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="5" max="5" width="51.8090909090909" customWidth="1"/>
-    <col min="6" max="6" width="17.4818181818182" customWidth="1"/>
-    <col min="7" max="7" width="16.7818181818182" customWidth="1"/>
-    <col min="8" max="8" width="14.1272727272727"/>
+    <col min="5" max="5" width="51.8083333333333" customWidth="1"/>
+    <col min="6" max="6" width="17.4833333333333" customWidth="1"/>
+    <col min="7" max="7" width="16.7833333333333" customWidth="1"/>
+    <col min="8" max="8" width="14.125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:13">
-      <c r="A2" s="12">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="13" t="s">
+      <c r="D2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="13">
         <v>45840</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="15">
         <v>20263300215</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="15" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="12"/>
+      <c r="M2" s="11"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:13">
-      <c r="A3" s="17">
+      <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="18" t="s">
+      <c r="D3" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="18">
         <v>45842</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="18">
         <v>45900</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:13">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>4</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="D4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="13">
         <v>45848</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="13">
         <v>45918</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="12"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:13">
-      <c r="A5" s="12">
+      <c r="M4" s="11"/>
+    </row>
+    <row r="5" s="3" customFormat="1" spans="1:13">
+      <c r="A5" s="20">
         <v>5</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="49" t="s">
+      <c r="D5" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="20"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:13">
-      <c r="A6" s="21">
+      <c r="A6" s="20">
         <v>6</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="20" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23" t="s">
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="21" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
     </row>
     <row r="7" s="3" customFormat="1" spans="1:13">
-      <c r="A7" s="21">
+      <c r="A7" s="20">
         <v>7</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="20" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="23">
         <v>45874</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="23">
         <v>45897</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="21">
         <v>20263300074</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="21" t="s">
         <v>18</v>
       </c>
       <c r="J7" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="K7" s="21" t="s">
+      <c r="K7" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:13">
-      <c r="A8" s="21">
+      <c r="A8" s="20">
         <v>8</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="23">
         <v>45864</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="23">
         <v>45920</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="21">
         <v>26002158</v>
       </c>
-      <c r="I8" s="23" t="s">
+      <c r="I8" s="21" t="s">
         <v>18</v>
       </c>
       <c r="J8" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:13">
-      <c r="A9" s="21">
+      <c r="A9" s="20">
         <v>9</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="20" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="23">
         <v>45867</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="23">
         <v>45879</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="21">
         <v>20263308927</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="53" t="s">
+      <c r="J9" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
     </row>
     <row r="10" s="4" customFormat="1" spans="1:13">
-      <c r="A10" s="25">
+      <c r="A10" s="24">
         <v>10</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="26" t="s">
+      <c r="D10" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="26">
         <v>45857</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="26">
         <v>45901</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="28" t="s">
+      <c r="I10" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="26" t="s">
+      <c r="J10" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
     </row>
     <row r="11" s="5" customFormat="1" spans="1:13">
-      <c r="A11" s="29">
+      <c r="A11" s="28">
         <v>11</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="30" t="s">
+      <c r="D11" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31" t="s">
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="31" t="s">
+      <c r="I11" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="30" t="s">
+      <c r="J11" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="K11" s="29" t="s">
+      <c r="K11" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="29" t="s">
+      <c r="L11" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="29" t="s">
+      <c r="M11" s="28" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:13">
-      <c r="A12" s="17">
+      <c r="A12" s="16">
         <v>12</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="20" t="s">
+      <c r="D12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="K12" s="17" t="s">
+      <c r="K12" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
     </row>
     <row r="13" s="5" customFormat="1" spans="1:13">
-      <c r="A13" s="29">
+      <c r="A13" s="28">
         <v>13</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31">
+      <c r="D13" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="28"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30">
         <v>20263301375</v>
       </c>
-      <c r="I13" s="31" t="s">
+      <c r="I13" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="30" t="s">
+      <c r="J13" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="33">
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+    </row>
+    <row r="14" s="6" customFormat="1" spans="1:13">
+      <c r="A14" s="32">
         <v>14</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="34" t="s">
+      <c r="D14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="33">
         <v>45871</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="33">
         <v>45919</v>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="34">
         <v>20262200196</v>
       </c>
-      <c r="I14" s="36" t="s">
+      <c r="I14" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="34" t="s">
+      <c r="J14" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:13">
-      <c r="A15" s="17">
-        <v>15</v>
-      </c>
-      <c r="B15" s="17" t="s">
+      <c r="A15" s="16">
+        <v>15</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="18" t="s">
+      <c r="D15" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="31">
         <v>45839</v>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="31">
         <v>45910</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="I15" s="20" t="s">
+      <c r="I15" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="J15" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="33">
+      <c r="A16" s="35">
         <v>16</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="34" t="s">
+      <c r="D16" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="36" t="s">
         <v>81</v>
       </c>
       <c r="F16" s="37">
@@ -2365,30 +2359,30 @@
       <c r="G16" s="37">
         <v>45897</v>
       </c>
-      <c r="H16" s="33">
+      <c r="H16" s="35">
         <v>202601506</v>
       </c>
-      <c r="I16" s="33" t="s">
+      <c r="I16" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="34" t="s">
+      <c r="J16" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:13">
-      <c r="A17" s="21">
+      <c r="A17" s="20">
         <v>17</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="20" t="s">
         <v>15</v>
       </c>
       <c r="E17" s="22" t="s">
@@ -2400,20 +2394,20 @@
       <c r="G17" s="38">
         <v>45916</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="20">
         <v>20263312838</v>
       </c>
-      <c r="I17" s="21" t="s">
+      <c r="I17" s="20" t="s">
         <v>18</v>
       </c>
       <c r="J17" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-    </row>
-    <row r="18" s="6" customFormat="1" spans="1:13">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+    </row>
+    <row r="18" s="7" customFormat="1" spans="1:13">
       <c r="A18" s="39">
         <v>18</v>
       </c>
@@ -2444,116 +2438,116 @@
       <c r="L18" s="39"/>
       <c r="M18" s="39"/>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="33">
+    <row r="19" s="6" customFormat="1" spans="1:13">
+      <c r="A19" s="32">
         <v>19</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="41" t="s">
+      <c r="D19" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="41">
         <v>45901</v>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="41">
         <v>45915</v>
       </c>
-      <c r="H19" s="33" t="s">
+      <c r="H19" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="I19" s="33" t="s">
+      <c r="I19" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="34" t="s">
+      <c r="J19" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:13">
-      <c r="A20" s="12">
+      <c r="A20" s="11">
         <v>20</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12" t="s">
+      <c r="D20" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-    </row>
-    <row r="21" s="6" customFormat="1" spans="1:13">
-      <c r="A21" s="39">
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+    </row>
+    <row r="21" s="3" customFormat="1" spans="1:13">
+      <c r="A21" s="20">
         <v>21</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="40" t="s">
+      <c r="D21" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="42">
+      <c r="F21" s="38">
         <v>45903</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="38">
         <v>45912</v>
       </c>
-      <c r="H21" s="39" t="s">
+      <c r="H21" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="39" t="s">
+      <c r="I21" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="J21" s="40" t="s">
+      <c r="J21" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:13">
-      <c r="A22" s="21">
+      <c r="A22" s="20">
         <v>19</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="20" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="22" t="s">
@@ -2565,68 +2559,68 @@
       <c r="G22" s="38">
         <v>45915</v>
       </c>
-      <c r="H22" s="21" t="s">
+      <c r="H22" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="I22" s="21" t="s">
+      <c r="I22" s="20" t="s">
         <v>18</v>
       </c>
       <c r="J22" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="33">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+    </row>
+    <row r="23" s="6" customFormat="1" spans="1:13">
+      <c r="A23" s="32">
         <v>19</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="34" t="s">
+      <c r="D23" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="37">
+      <c r="F23" s="41">
         <v>45901</v>
       </c>
-      <c r="G23" s="37">
+      <c r="G23" s="41">
         <v>45915</v>
       </c>
-      <c r="H23" s="33" t="s">
+      <c r="H23" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="I23" s="33" t="s">
+      <c r="I23" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J23" s="34" t="s">
+      <c r="J23" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="33">
+      <c r="A24" s="35">
         <v>24</v>
       </c>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="41" t="s">
+      <c r="D24" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="42" t="s">
         <v>103</v>
       </c>
       <c r="F24" s="37">
@@ -2635,20 +2629,20 @@
       <c r="G24" s="37">
         <v>45903</v>
       </c>
-      <c r="H24" s="33">
+      <c r="H24" s="35">
         <v>20253305016</v>
       </c>
-      <c r="I24" s="33" t="s">
+      <c r="I24" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="J24" s="34" t="s">
+      <c r="J24" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-    </row>
-    <row r="25" s="7" customFormat="1" spans="1:13">
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+    </row>
+    <row r="25" s="8" customFormat="1" spans="1:13">
       <c r="A25" s="43">
         <v>25</v>
       </c>
@@ -2678,17 +2672,17 @@
       <c r="M25" s="43"/>
     </row>
     <row r="26" s="5" customFormat="1" spans="1:13">
-      <c r="A26" s="29">
+      <c r="A26" s="28">
         <v>26</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="30" t="s">
+      <c r="C26" s="28"/>
+      <c r="D26" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="29" t="s">
         <v>109</v>
       </c>
       <c r="F26" s="46">
@@ -2697,33 +2691,33 @@
       <c r="G26" s="46">
         <v>45919</v>
       </c>
-      <c r="H26" s="29" t="s">
+      <c r="H26" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="I26" s="29" t="s">
+      <c r="I26" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="J26" s="30" t="s">
+      <c r="J26" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:13">
-      <c r="A27" s="12">
+      <c r="A27" s="11">
         <v>27</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="13" t="s">
+      <c r="D27" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>112</v>
       </c>
       <c r="F27" s="47">
@@ -2732,57 +2726,57 @@
       <c r="G27" s="47">
         <v>45915</v>
       </c>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="13" t="s">
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
     </row>
     <row r="28" s="5" customFormat="1" spans="1:13">
-      <c r="A28" s="29">
+      <c r="A28" s="28">
         <v>28</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="30" t="s">
+      <c r="D28" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="12" t="s">
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J28" s="30" t="s">
+      <c r="J28" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:13">
-      <c r="A29" s="12">
+      <c r="A29" s="11">
         <v>29</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="48" t="s">
@@ -2794,34 +2788,34 @@
       <c r="G29" s="47">
         <v>45915</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="H29" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="12" t="s">
+      <c r="I29" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J29" s="13" t="s">
+      <c r="J29" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="K29" s="12" t="s">
+      <c r="K29" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L29" s="12" t="s">
+      <c r="L29" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="M29" s="12"/>
+      <c r="M29" s="11"/>
     </row>
     <row r="30" s="3" customFormat="1" spans="1:13">
-      <c r="A30" s="21">
+      <c r="A30" s="20">
         <v>30</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="20" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="22" t="s">
@@ -2833,30 +2827,30 @@
       <c r="G30" s="38">
         <v>45910</v>
       </c>
-      <c r="H30" s="21" t="s">
+      <c r="H30" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="I30" s="21" t="s">
+      <c r="I30" s="20" t="s">
         <v>18</v>
       </c>
       <c r="J30" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
     </row>
     <row r="31" s="3" customFormat="1" spans="1:13">
-      <c r="A31" s="21">
+      <c r="A31" s="20">
         <v>31</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="20" t="s">
         <v>15</v>
       </c>
       <c r="E31" s="22" t="s">
@@ -2868,67 +2862,67 @@
       <c r="G31" s="38">
         <v>45910</v>
       </c>
-      <c r="H31" s="21" t="s">
+      <c r="H31" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="I31" s="21" t="s">
+      <c r="I31" s="20" t="s">
         <v>18</v>
       </c>
       <c r="J31" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21" t="s">
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="32" s="6" customFormat="1" spans="1:13">
-      <c r="A32" s="39">
+    <row r="32" s="5" customFormat="1" spans="1:13">
+      <c r="A32" s="28">
         <v>32</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="40" t="s">
+      <c r="D32" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="F32" s="42">
+      <c r="F32" s="46">
         <v>45903</v>
       </c>
-      <c r="G32" s="42">
+      <c r="G32" s="46">
         <v>45915</v>
       </c>
-      <c r="H32" s="39">
+      <c r="H32" s="28">
         <v>20263304452</v>
       </c>
-      <c r="I32" s="39" t="s">
+      <c r="I32" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="J32" s="40" t="s">
+      <c r="J32" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="K32" s="39"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="39"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:13">
-      <c r="A33" s="12">
+      <c r="A33" s="11">
         <v>33</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E33" s="49" t="s">
@@ -2940,35 +2934,35 @@
       <c r="G33" s="47">
         <v>45909</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="11">
         <v>20263311417</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="I33" s="11" t="s">
         <v>18</v>
       </c>
       <c r="J33" s="49" t="s">
         <v>133</v>
       </c>
-      <c r="K33" s="12" t="s">
+      <c r="K33" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L33" s="12" t="s">
+      <c r="L33" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="M33" s="12"/>
+      <c r="M33" s="11"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="33">
+      <c r="A34" s="35">
         <v>34</v>
       </c>
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="33"/>
-      <c r="E34" s="41" t="s">
+      <c r="D34" s="35"/>
+      <c r="E34" s="42" t="s">
         <v>135</v>
       </c>
       <c r="F34" s="37">
@@ -2977,63 +2971,63 @@
       <c r="G34" s="37">
         <v>45910</v>
       </c>
-      <c r="H34" s="33" t="s">
+      <c r="H34" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="I34" s="33" t="s">
+      <c r="I34" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="J34" s="34" t="s">
+      <c r="J34" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:13">
-      <c r="A35" s="12">
+      <c r="A35" s="11">
         <v>35</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12">
+      <c r="D35" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11">
         <v>202608849</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="I35" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J35" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="K35" s="12" t="s">
+      <c r="K35" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L35" s="12" t="s">
+      <c r="L35" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="M35" s="12"/>
+      <c r="M35" s="11"/>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:13">
-      <c r="A36" s="21">
+      <c r="A36" s="20">
         <v>36</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="20" t="s">
         <v>15</v>
       </c>
       <c r="E36" s="22" t="s">
@@ -3045,62 +3039,62 @@
       <c r="G36" s="38">
         <v>45912</v>
       </c>
-      <c r="H36" s="21">
+      <c r="H36" s="20">
         <v>20263327091</v>
       </c>
-      <c r="I36" s="21" t="s">
+      <c r="I36" s="20" t="s">
         <v>18</v>
       </c>
       <c r="J36" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="21"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:13">
-      <c r="A37" s="12">
+      <c r="A37" s="11">
         <v>37</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D37" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12" t="s">
+      <c r="D37" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="I37" s="11" t="s">
         <v>18</v>
       </c>
       <c r="J37" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="12"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
     </row>
     <row r="38" s="5" customFormat="1" spans="1:13">
-      <c r="A38" s="29">
+      <c r="A38" s="28">
         <v>38</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="30" t="s">
+      <c r="D38" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="29" t="s">
         <v>151</v>
       </c>
       <c r="F38" s="46">
@@ -3109,15 +3103,15 @@
       <c r="G38" s="46">
         <v>45913</v>
       </c>
-      <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="29"/>
-      <c r="M38" s="29"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="33">
+      <c r="A39" s="35">
         <v>39</v>
       </c>
       <c r="B39" s="43" t="s">
@@ -3148,23 +3142,23 @@
       <c r="K39" s="43"/>
       <c r="L39" s="43"/>
       <c r="M39" s="43"/>
-      <c r="N39" s="7"/>
-      <c r="O39" s="7"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:13">
-      <c r="A40" s="12">
+      <c r="A40" s="11">
         <v>40</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="13" t="s">
+      <c r="D40" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="12" t="s">
         <v>156</v>
       </c>
       <c r="F40" s="47">
@@ -3173,29 +3167,29 @@
       <c r="G40" s="47">
         <v>45921</v>
       </c>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="13" t="s">
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="K40" s="12"/>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
-    </row>
-    <row r="41" s="7" customFormat="1" spans="1:15">
-      <c r="A41" s="33">
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+    </row>
+    <row r="41" s="8" customFormat="1" spans="1:15">
+      <c r="A41" s="35">
         <v>41</v>
       </c>
-      <c r="B41" s="33" t="s">
+      <c r="B41" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="C41" s="33" t="s">
+      <c r="C41" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="D41" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="34" t="s">
+      <c r="D41" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="36" t="s">
         <v>160</v>
       </c>
       <c r="F41" s="37">
@@ -3204,35 +3198,35 @@
       <c r="G41" s="37">
         <v>45916</v>
       </c>
-      <c r="H41" s="33" t="s">
+      <c r="H41" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="33" t="s">
+      <c r="I41" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="J41" s="34" t="s">
+      <c r="J41" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="K41" s="33"/>
-      <c r="L41" s="33"/>
-      <c r="M41" s="33"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="35"/>
       <c r="N41"/>
       <c r="O41"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="33">
+      <c r="A42" s="35">
         <v>42</v>
       </c>
-      <c r="B42" s="33" t="s">
+      <c r="B42" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="C42" s="33" t="s">
+      <c r="C42" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="D42" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" s="41" t="s">
+      <c r="D42" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="42" t="s">
         <v>164</v>
       </c>
       <c r="F42" s="37">
@@ -3241,109 +3235,109 @@
       <c r="G42" s="37">
         <v>45922</v>
       </c>
-      <c r="H42" s="33">
+      <c r="H42" s="35">
         <v>202601040</v>
       </c>
-      <c r="I42" s="33" t="s">
+      <c r="I42" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="J42" s="41" t="s">
+      <c r="J42" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="33"/>
+      <c r="K42" s="35"/>
+      <c r="L42" s="35"/>
+      <c r="M42" s="35"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:13">
-      <c r="A43" s="12">
+      <c r="A43" s="11">
         <v>43</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12">
+      <c r="D43" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11">
         <v>20263309395</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="I43" s="11" t="s">
         <v>18</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K43" s="12"/>
-      <c r="L43" s="12"/>
-      <c r="M43" s="12"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="33">
+      <c r="A44" s="35">
         <v>44</v>
       </c>
-      <c r="B44" s="33" t="s">
+      <c r="B44" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="C44" s="33" t="s">
+      <c r="C44" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="D44" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="33"/>
-      <c r="M44" s="33" t="s">
+      <c r="D44" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="35"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="35"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="35"/>
+      <c r="L44" s="35"/>
+      <c r="M44" s="35" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="45" s="8" customFormat="1" spans="1:13">
-      <c r="A45" s="50">
+    <row r="45" s="3" customFormat="1" spans="1:13">
+      <c r="A45" s="20">
         <v>45</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C45" s="21" t="s">
+      <c r="C45" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D45" s="20" t="s">
         <v>15</v>
       </c>
       <c r="E45" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="F45" s="51">
+      <c r="F45" s="38">
         <v>45912</v>
       </c>
-      <c r="G45" s="51">
+      <c r="G45" s="38">
         <v>45915</v>
       </c>
-      <c r="H45" s="21" t="s">
+      <c r="H45" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="I45" s="21" t="s">
+      <c r="I45" s="20" t="s">
         <v>18</v>
       </c>
       <c r="J45" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="K45" s="50"/>
-      <c r="L45" s="50"/>
-      <c r="M45" s="50"/>
-    </row>
-    <row r="46" s="6" customFormat="1" spans="1:13">
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+    </row>
+    <row r="46" s="7" customFormat="1" spans="1:13">
       <c r="A46" s="39">
         <v>46</v>
       </c>
@@ -3359,10 +3353,10 @@
       <c r="E46" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="F46" s="42">
+      <c r="F46" s="50">
         <v>45915</v>
       </c>
-      <c r="G46" s="42">
+      <c r="G46" s="50">
         <v>45920</v>
       </c>
       <c r="H46" s="39"/>
@@ -3374,105 +3368,105 @@
         <v>169</v>
       </c>
     </row>
-    <row r="47" s="9" customFormat="1" spans="1:13">
-      <c r="A47" s="52">
+    <row r="47" s="1" customFormat="1" spans="1:13">
+      <c r="A47" s="11">
         <v>47</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D47" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="52"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="52"/>
-      <c r="L47" s="52"/>
-      <c r="M47" s="12" t="s">
+      <c r="D47" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:13">
-      <c r="A48" s="12">
+      <c r="A48" s="11">
         <v>48</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D48" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E48" s="13" t="s">
+      <c r="D48" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12" t="s">
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I48" s="12" t="s">
+      <c r="I48" s="11" t="s">
         <v>18</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
-      <c r="M48" s="12"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="33">
+      <c r="A49" s="35">
         <v>49</v>
       </c>
-      <c r="B49" s="33" t="s">
+      <c r="B49" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="C49" s="33" t="s">
+      <c r="C49" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="D49" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="33"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="33"/>
-      <c r="H49" s="12" t="s">
+      <c r="D49" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="35"/>
+      <c r="F49" s="35"/>
+      <c r="G49" s="35"/>
+      <c r="H49" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I49" s="12" t="s">
+      <c r="I49" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J49" s="41" t="s">
+      <c r="J49" s="42" t="s">
         <v>180</v>
       </c>
-      <c r="K49" s="33"/>
-      <c r="L49" s="33"/>
-      <c r="M49" s="33"/>
+      <c r="K49" s="35"/>
+      <c r="L49" s="35"/>
+      <c r="M49" s="35"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="33">
+      <c r="A50" s="35">
         <v>50</v>
       </c>
-      <c r="B50" s="33" t="s">
+      <c r="B50" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="C50" s="33" t="s">
+      <c r="C50" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="D50" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="41" t="s">
+      <c r="D50" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="42" t="s">
         <v>182</v>
       </c>
       <c r="F50" s="37">
@@ -3481,330 +3475,330 @@
       <c r="G50" s="37">
         <v>45915</v>
       </c>
-      <c r="H50" s="33">
+      <c r="H50" s="35">
         <v>2513269</v>
       </c>
-      <c r="I50" s="33" t="s">
+      <c r="I50" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
-      <c r="L50" s="33"/>
-      <c r="M50" s="33"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="35"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="35"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="33">
+      <c r="A51" s="35">
         <v>51</v>
       </c>
-      <c r="B51" s="33" t="s">
+      <c r="B51" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="C51" s="33" t="s">
+      <c r="C51" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="D51" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="12" t="s">
+      <c r="D51" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I51" s="12" t="s">
+      <c r="I51" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J51" s="41" t="s">
+      <c r="J51" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="K51" s="33"/>
-      <c r="L51" s="33"/>
-      <c r="M51" s="33"/>
+      <c r="K51" s="35"/>
+      <c r="L51" s="35"/>
+      <c r="M51" s="35"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="33"/>
-      <c r="B52" s="33"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="33"/>
-      <c r="G52" s="33"/>
-      <c r="H52" s="33"/>
-      <c r="I52" s="33"/>
-      <c r="J52" s="33"/>
-      <c r="K52" s="33"/>
-      <c r="L52" s="33"/>
-      <c r="M52" s="33"/>
+      <c r="A52" s="35"/>
+      <c r="B52" s="35"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
+      <c r="M52" s="35"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="33"/>
-      <c r="B53" s="33"/>
-      <c r="C53" s="33"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="33"/>
-      <c r="J53" s="33"/>
-      <c r="K53" s="33"/>
-      <c r="L53" s="33"/>
-      <c r="M53" s="33"/>
+      <c r="A53" s="35"/>
+      <c r="B53" s="35"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="33"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="33"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="33"/>
-      <c r="L54" s="33"/>
-      <c r="M54" s="33"/>
+      <c r="A54" s="35"/>
+      <c r="B54" s="35"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="35"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="35"/>
+      <c r="J54" s="35"/>
+      <c r="K54" s="35"/>
+      <c r="L54" s="35"/>
+      <c r="M54" s="35"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="33"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="33"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
-      <c r="F55" s="33"/>
-      <c r="G55" s="33"/>
-      <c r="H55" s="33"/>
-      <c r="I55" s="33"/>
-      <c r="J55" s="33"/>
-      <c r="K55" s="33"/>
-      <c r="L55" s="33"/>
-      <c r="M55" s="33"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
+      <c r="G55" s="35"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="35"/>
+      <c r="J55" s="35"/>
+      <c r="K55" s="35"/>
+      <c r="L55" s="35"/>
+      <c r="M55" s="35"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="33"/>
-      <c r="B56" s="33"/>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="33"/>
-      <c r="F56" s="33"/>
-      <c r="G56" s="33"/>
-      <c r="H56" s="33"/>
-      <c r="I56" s="33"/>
-      <c r="J56" s="33"/>
-      <c r="K56" s="33"/>
-      <c r="L56" s="33"/>
-      <c r="M56" s="33"/>
+      <c r="A56" s="35"/>
+      <c r="B56" s="35"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="35"/>
+      <c r="J56" s="35"/>
+      <c r="K56" s="35"/>
+      <c r="L56" s="35"/>
+      <c r="M56" s="35"/>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="33"/>
-      <c r="B57" s="33"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="33"/>
-      <c r="F57" s="33"/>
-      <c r="G57" s="33"/>
-      <c r="H57" s="33"/>
-      <c r="I57" s="33"/>
-      <c r="J57" s="33"/>
-      <c r="K57" s="33"/>
-      <c r="L57" s="33"/>
-      <c r="M57" s="33"/>
+      <c r="A57" s="35"/>
+      <c r="B57" s="35"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="35"/>
+      <c r="L57" s="35"/>
+      <c r="M57" s="35"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="33"/>
-      <c r="B58" s="33"/>
-      <c r="C58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
-      <c r="F58" s="33"/>
-      <c r="G58" s="33"/>
-      <c r="H58" s="33"/>
-      <c r="I58" s="33"/>
-      <c r="J58" s="33"/>
-      <c r="K58" s="33"/>
-      <c r="L58" s="33"/>
-      <c r="M58" s="33"/>
+      <c r="A58" s="35"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="35"/>
+      <c r="M58" s="35"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="33"/>
-      <c r="B59" s="33"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="33"/>
-      <c r="H59" s="33"/>
-      <c r="I59" s="33"/>
-      <c r="J59" s="33"/>
-      <c r="K59" s="33"/>
-      <c r="L59" s="33"/>
-      <c r="M59" s="33"/>
+      <c r="A59" s="35"/>
+      <c r="B59" s="35"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
+      <c r="L59" s="35"/>
+      <c r="M59" s="35"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="33"/>
-      <c r="B60" s="33"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="33"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="33"/>
-      <c r="J60" s="33"/>
-      <c r="K60" s="33"/>
-      <c r="L60" s="33"/>
-      <c r="M60" s="33"/>
+      <c r="A60" s="35"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="35"/>
+      <c r="I60" s="35"/>
+      <c r="J60" s="35"/>
+      <c r="K60" s="35"/>
+      <c r="L60" s="35"/>
+      <c r="M60" s="35"/>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="33"/>
-      <c r="B61" s="33"/>
-      <c r="C61" s="33"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="33"/>
-      <c r="F61" s="33"/>
-      <c r="G61" s="33"/>
-      <c r="H61" s="33"/>
-      <c r="I61" s="33"/>
-      <c r="J61" s="33"/>
-      <c r="K61" s="33"/>
-      <c r="L61" s="33"/>
-      <c r="M61" s="33"/>
+      <c r="A61" s="35"/>
+      <c r="B61" s="35"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="35"/>
+      <c r="I61" s="35"/>
+      <c r="J61" s="35"/>
+      <c r="K61" s="35"/>
+      <c r="L61" s="35"/>
+      <c r="M61" s="35"/>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="33"/>
-      <c r="B62" s="33"/>
-      <c r="C62" s="33"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="33"/>
-      <c r="F62" s="33"/>
-      <c r="G62" s="33"/>
-      <c r="H62" s="33"/>
-      <c r="I62" s="33"/>
-      <c r="J62" s="33"/>
-      <c r="K62" s="33"/>
-      <c r="L62" s="33"/>
-      <c r="M62" s="33"/>
+      <c r="A62" s="35"/>
+      <c r="B62" s="35"/>
+      <c r="C62" s="35"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="35"/>
+      <c r="J62" s="35"/>
+      <c r="K62" s="35"/>
+      <c r="L62" s="35"/>
+      <c r="M62" s="35"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="33"/>
-      <c r="B63" s="33"/>
-      <c r="C63" s="33"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="33"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="33"/>
-      <c r="L63" s="33"/>
-      <c r="M63" s="33"/>
+      <c r="A63" s="35"/>
+      <c r="B63" s="35"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35"/>
+      <c r="I63" s="35"/>
+      <c r="J63" s="35"/>
+      <c r="K63" s="35"/>
+      <c r="L63" s="35"/>
+      <c r="M63" s="35"/>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="33"/>
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
-      <c r="E64" s="33"/>
-      <c r="F64" s="33"/>
-      <c r="G64" s="33"/>
-      <c r="H64" s="33"/>
-      <c r="I64" s="33"/>
-      <c r="J64" s="33"/>
-      <c r="K64" s="33"/>
-      <c r="L64" s="33"/>
-      <c r="M64" s="33"/>
+      <c r="A64" s="35"/>
+      <c r="B64" s="35"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35"/>
+      <c r="I64" s="35"/>
+      <c r="J64" s="35"/>
+      <c r="K64" s="35"/>
+      <c r="L64" s="35"/>
+      <c r="M64" s="35"/>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="33"/>
-      <c r="B65" s="33"/>
-      <c r="C65" s="33"/>
-      <c r="D65" s="33"/>
-      <c r="E65" s="33"/>
-      <c r="F65" s="33"/>
-      <c r="G65" s="33"/>
-      <c r="H65" s="33"/>
-      <c r="I65" s="33"/>
-      <c r="J65" s="33"/>
-      <c r="K65" s="33"/>
-      <c r="L65" s="33"/>
-      <c r="M65" s="33"/>
+      <c r="A65" s="35"/>
+      <c r="B65" s="35"/>
+      <c r="C65" s="35"/>
+      <c r="D65" s="35"/>
+      <c r="E65" s="35"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="35"/>
+      <c r="I65" s="35"/>
+      <c r="J65" s="35"/>
+      <c r="K65" s="35"/>
+      <c r="L65" s="35"/>
+      <c r="M65" s="35"/>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="33"/>
-      <c r="B66" s="33"/>
-      <c r="C66" s="33"/>
-      <c r="D66" s="33"/>
-      <c r="E66" s="33"/>
-      <c r="F66" s="33"/>
-      <c r="G66" s="33"/>
-      <c r="H66" s="33"/>
-      <c r="I66" s="33"/>
-      <c r="J66" s="33"/>
-      <c r="K66" s="33"/>
-      <c r="L66" s="33"/>
-      <c r="M66" s="33"/>
+      <c r="A66" s="35"/>
+      <c r="B66" s="35"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="35"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="35"/>
+      <c r="I66" s="35"/>
+      <c r="J66" s="35"/>
+      <c r="K66" s="35"/>
+      <c r="L66" s="35"/>
+      <c r="M66" s="35"/>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="33"/>
-      <c r="B67" s="33"/>
-      <c r="C67" s="33"/>
-      <c r="D67" s="33"/>
-      <c r="E67" s="33"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="33"/>
-      <c r="H67" s="33"/>
-      <c r="I67" s="33"/>
-      <c r="J67" s="33"/>
-      <c r="K67" s="33"/>
-      <c r="L67" s="33"/>
-      <c r="M67" s="33"/>
+      <c r="A67" s="35"/>
+      <c r="B67" s="35"/>
+      <c r="C67" s="35"/>
+      <c r="D67" s="35"/>
+      <c r="E67" s="35"/>
+      <c r="F67" s="35"/>
+      <c r="G67" s="35"/>
+      <c r="H67" s="35"/>
+      <c r="I67" s="35"/>
+      <c r="J67" s="35"/>
+      <c r="K67" s="35"/>
+      <c r="L67" s="35"/>
+      <c r="M67" s="35"/>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="33"/>
-      <c r="B68" s="33"/>
-      <c r="C68" s="33"/>
-      <c r="D68" s="33"/>
-      <c r="E68" s="33"/>
-      <c r="F68" s="33"/>
-      <c r="G68" s="33"/>
-      <c r="H68" s="33"/>
-      <c r="I68" s="33"/>
-      <c r="J68" s="33"/>
-      <c r="K68" s="33"/>
-      <c r="L68" s="33"/>
-      <c r="M68" s="33"/>
+      <c r="A68" s="35"/>
+      <c r="B68" s="35"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="35"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="35"/>
+      <c r="I68" s="35"/>
+      <c r="J68" s="35"/>
+      <c r="K68" s="35"/>
+      <c r="L68" s="35"/>
+      <c r="M68" s="35"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="33"/>
-      <c r="B69" s="33"/>
-      <c r="C69" s="33"/>
-      <c r="D69" s="33"/>
-      <c r="E69" s="33"/>
-      <c r="F69" s="33"/>
-      <c r="G69" s="33"/>
-      <c r="H69" s="33"/>
-      <c r="I69" s="33"/>
-      <c r="J69" s="33"/>
-      <c r="K69" s="33"/>
-      <c r="L69" s="33"/>
-      <c r="M69" s="33"/>
+      <c r="A69" s="35"/>
+      <c r="B69" s="35"/>
+      <c r="C69" s="35"/>
+      <c r="D69" s="35"/>
+      <c r="E69" s="35"/>
+      <c r="F69" s="35"/>
+      <c r="G69" s="35"/>
+      <c r="H69" s="35"/>
+      <c r="I69" s="35"/>
+      <c r="J69" s="35"/>
+      <c r="K69" s="35"/>
+      <c r="L69" s="35"/>
+      <c r="M69" s="35"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="33"/>
-      <c r="B70" s="33"/>
-      <c r="C70" s="33"/>
-      <c r="D70" s="33"/>
-      <c r="E70" s="33"/>
-      <c r="F70" s="33"/>
-      <c r="G70" s="33"/>
-      <c r="H70" s="33"/>
-      <c r="I70" s="33"/>
-      <c r="J70" s="33"/>
-      <c r="K70" s="33"/>
-      <c r="L70" s="33"/>
-      <c r="M70" s="33"/>
+      <c r="A70" s="35"/>
+      <c r="B70" s="35"/>
+      <c r="C70" s="35"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="35"/>
+      <c r="F70" s="35"/>
+      <c r="G70" s="35"/>
+      <c r="H70" s="35"/>
+      <c r="I70" s="35"/>
+      <c r="J70" s="35"/>
+      <c r="K70" s="35"/>
+      <c r="L70" s="35"/>
+      <c r="M70" s="35"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3902,7 +3896,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3914,7 +3908,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/预推免院校/汇总.xlsx
+++ b/预推免院校/汇总.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="186">
   <si>
     <t>序号</t>
   </si>
@@ -431,6 +431,9 @@
   </si>
   <si>
     <t>https://yzss.hhu.edu.cn/logon</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>软件研究所</t>
@@ -1331,7 +1334,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1348,9 +1351,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1428,15 +1428,9 @@
     <xf numFmtId="58" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1453,9 +1447,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="6" applyBorder="1">
@@ -1817,1988 +1808,1988 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:13">
-      <c r="A2" s="11">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="12" t="s">
+      <c r="D2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="12">
         <v>45840</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="14">
         <v>20263300215</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="14" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="11"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:13">
-      <c r="A3" s="16">
+      <c r="A3" s="15">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="17">
         <v>45842</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="17">
         <v>45900</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:13">
-      <c r="A4" s="11">
+      <c r="A4" s="10">
         <v>4</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="12" t="s">
+      <c r="D4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>45848</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>45918</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="11"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" s="3" customFormat="1" spans="1:13">
-      <c r="A5" s="20">
+      <c r="A5" s="19">
         <v>5</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22" t="s">
+      <c r="D5" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="19"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:13">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>6</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="22" t="s">
+      <c r="D6" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21" t="s">
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="J6" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
     </row>
     <row r="7" s="3" customFormat="1" spans="1:13">
-      <c r="A7" s="20">
+      <c r="A7" s="19">
         <v>7</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="22" t="s">
+      <c r="D7" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="22">
         <v>45874</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>45897</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="20">
         <v>20263300074</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="J7" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="K7" s="20" t="s">
+      <c r="K7" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:13">
-      <c r="A8" s="20">
+      <c r="A8" s="19">
         <v>8</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="22" t="s">
+      <c r="D8" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="22">
         <v>45864</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="22">
         <v>45920</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="20">
         <v>26002158</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="22" t="s">
+      <c r="J8" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:13">
-      <c r="A9" s="20">
+      <c r="A9" s="19">
         <v>9</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="22" t="s">
+      <c r="D9" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="22">
         <v>45867</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="22">
         <v>45879</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="20">
         <v>20263308927</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="51" t="s">
+      <c r="J9" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
     </row>
     <row r="10" s="4" customFormat="1" spans="1:13">
-      <c r="A10" s="24">
+      <c r="A10" s="23">
         <v>10</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="25" t="s">
+      <c r="D10" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="25">
         <v>45857</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="25">
         <v>45901</v>
       </c>
-      <c r="H10" s="27" t="s">
+      <c r="H10" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="27" t="s">
+      <c r="I10" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
     </row>
     <row r="11" s="5" customFormat="1" spans="1:13">
-      <c r="A11" s="28">
+      <c r="A11" s="27">
         <v>11</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="29" t="s">
+      <c r="D11" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30" t="s">
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="30" t="s">
+      <c r="I11" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="29" t="s">
+      <c r="J11" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="K11" s="28" t="s">
+      <c r="K11" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="28" t="s">
+      <c r="L11" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="28" t="s">
+      <c r="M11" s="27" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:13">
-      <c r="A12" s="16">
+      <c r="A12" s="15">
         <v>12</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="19" t="s">
+      <c r="D12" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="19" t="s">
+      <c r="I12" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
     </row>
     <row r="13" s="5" customFormat="1" spans="1:13">
-      <c r="A13" s="28">
+      <c r="A13" s="27">
         <v>13</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30">
+      <c r="D13" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="27"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29">
         <v>20263301375</v>
       </c>
-      <c r="I13" s="30" t="s">
+      <c r="I13" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="29" t="s">
+      <c r="J13" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-    </row>
-    <row r="14" s="6" customFormat="1" spans="1:13">
-      <c r="A14" s="32">
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+    </row>
+    <row r="14" s="3" customFormat="1" spans="1:13">
+      <c r="A14" s="19">
         <v>14</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="22" t="s">
+      <c r="D14" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="31">
         <v>45871</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="31">
         <v>45919</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="20">
         <v>20262200196</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:13">
-      <c r="A15" s="16">
-        <v>15</v>
-      </c>
-      <c r="B15" s="16" t="s">
+      <c r="A15" s="15">
+        <v>15</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="17" t="s">
+      <c r="D15" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="30">
         <v>45839</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="30">
         <v>45910</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="I15" s="19" t="s">
+      <c r="I15" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="17" t="s">
+      <c r="J15" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="35">
+      <c r="A16" s="32">
         <v>16</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="36" t="s">
+      <c r="D16" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="34">
         <v>45855</v>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="34">
         <v>45897</v>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="32">
         <v>202601506</v>
       </c>
-      <c r="I16" s="35" t="s">
+      <c r="I16" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="36" t="s">
+      <c r="J16" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:13">
-      <c r="A17" s="20">
+      <c r="A17" s="19">
         <v>17</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="22" t="s">
+      <c r="D17" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="35">
         <v>45886</v>
       </c>
-      <c r="G17" s="38">
+      <c r="G17" s="35">
         <v>45916</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="19">
         <v>20263312838</v>
       </c>
-      <c r="I17" s="20" t="s">
+      <c r="I17" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="22" t="s">
+      <c r="J17" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-    </row>
-    <row r="18" s="7" customFormat="1" spans="1:13">
-      <c r="A18" s="39">
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+    </row>
+    <row r="18" s="6" customFormat="1" spans="1:13">
+      <c r="A18" s="36">
         <v>18</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="40" t="s">
+      <c r="D18" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39" t="s">
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="I18" s="39" t="s">
+      <c r="I18" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="40" t="s">
+      <c r="J18" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-    </row>
-    <row r="19" s="6" customFormat="1" spans="1:13">
-      <c r="A19" s="32">
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+    </row>
+    <row r="19" s="3" customFormat="1" spans="1:13">
+      <c r="A19" s="19">
         <v>19</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="22" t="s">
+      <c r="D19" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="35">
         <v>45901</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="35">
         <v>45915</v>
       </c>
-      <c r="H19" s="20" t="s">
+      <c r="H19" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="I19" s="20" t="s">
+      <c r="I19" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="22" t="s">
+      <c r="J19" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:13">
-      <c r="A20" s="11">
+      <c r="A20" s="10">
         <v>20</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11" t="s">
+      <c r="D20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
     </row>
     <row r="21" s="3" customFormat="1" spans="1:13">
-      <c r="A21" s="20">
+      <c r="A21" s="19">
         <v>21</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="22" t="s">
+      <c r="D21" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="38">
+      <c r="F21" s="35">
         <v>45903</v>
       </c>
-      <c r="G21" s="38">
+      <c r="G21" s="35">
         <v>45912</v>
       </c>
-      <c r="H21" s="20" t="s">
+      <c r="H21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="20" t="s">
+      <c r="I21" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="J21" s="22" t="s">
+      <c r="J21" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:13">
-      <c r="A22" s="20">
+      <c r="A22" s="19">
         <v>19</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="22" t="s">
+      <c r="D22" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="35">
         <v>45901</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G22" s="35">
         <v>45915</v>
       </c>
-      <c r="H22" s="20" t="s">
+      <c r="H22" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="I22" s="20" t="s">
+      <c r="I22" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J22" s="22" t="s">
+      <c r="J22" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-    </row>
-    <row r="23" s="6" customFormat="1" spans="1:13">
-      <c r="A23" s="32">
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:13">
+      <c r="A23" s="19">
         <v>19</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="22" t="s">
+      <c r="D23" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="35">
         <v>45901</v>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="35">
         <v>45915</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="H23" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="I23" s="20" t="s">
+      <c r="I23" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J23" s="22" t="s">
+      <c r="J23" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="35">
+      <c r="A24" s="32">
         <v>24</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="B24" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="42" t="s">
+      <c r="D24" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="F24" s="37">
+      <c r="F24" s="34">
         <v>45871</v>
       </c>
-      <c r="G24" s="37">
+      <c r="G24" s="34">
         <v>45903</v>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="32">
         <v>20253305016</v>
       </c>
-      <c r="I24" s="35" t="s">
+      <c r="I24" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="J24" s="36" t="s">
+      <c r="J24" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-    </row>
-    <row r="25" s="8" customFormat="1" spans="1:13">
-      <c r="A25" s="43">
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+    </row>
+    <row r="25" s="7" customFormat="1" spans="1:13">
+      <c r="A25" s="39">
         <v>25</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="43" t="s">
+      <c r="D25" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="E25" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="F25" s="45">
+      <c r="F25" s="41">
         <v>45894</v>
       </c>
-      <c r="G25" s="45">
+      <c r="G25" s="41">
         <v>45912</v>
       </c>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
     </row>
     <row r="26" s="5" customFormat="1" spans="1:13">
-      <c r="A26" s="28">
+      <c r="A26" s="27">
         <v>26</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="29" t="s">
+      <c r="C26" s="27"/>
+      <c r="D26" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="F26" s="46">
+      <c r="F26" s="42">
         <v>45890</v>
       </c>
-      <c r="G26" s="46">
+      <c r="G26" s="42">
         <v>45919</v>
       </c>
-      <c r="H26" s="28" t="s">
+      <c r="H26" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="I26" s="28" t="s">
+      <c r="I26" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="J26" s="29" t="s">
+      <c r="J26" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:13">
-      <c r="A27" s="11">
+      <c r="A27" s="10">
         <v>27</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="12" t="s">
+      <c r="D27" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="F27" s="47">
+      <c r="F27" s="43">
         <v>45902</v>
       </c>
-      <c r="G27" s="47">
+      <c r="G27" s="43">
         <v>45915</v>
       </c>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="12" t="s">
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
     </row>
     <row r="28" s="5" customFormat="1" spans="1:13">
-      <c r="A28" s="28">
+      <c r="A28" s="27">
         <v>28</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="29" t="s">
+      <c r="D28" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="11" t="s">
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J28" s="29" t="s">
+      <c r="J28" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:13">
-      <c r="A29" s="11">
+      <c r="A29" s="10">
         <v>29</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="48" t="s">
+      <c r="D29" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="F29" s="47">
+      <c r="F29" s="43">
         <v>45902</v>
       </c>
-      <c r="G29" s="47">
+      <c r="G29" s="43">
         <v>45915</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J29" s="12" t="s">
+      <c r="J29" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="K29" s="11" t="s">
+      <c r="K29" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="L29" s="11" t="s">
+      <c r="L29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="M29" s="11"/>
+      <c r="M29" s="10"/>
     </row>
     <row r="30" s="3" customFormat="1" spans="1:13">
-      <c r="A30" s="20">
+      <c r="A30" s="19">
         <v>30</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D30" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="22" t="s">
+      <c r="D30" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="F30" s="38">
+      <c r="F30" s="35">
         <v>45902</v>
       </c>
-      <c r="G30" s="38">
+      <c r="G30" s="35">
         <v>45910</v>
       </c>
-      <c r="H30" s="20" t="s">
+      <c r="H30" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="I30" s="20" t="s">
+      <c r="I30" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J30" s="22" t="s">
+      <c r="J30" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
     </row>
     <row r="31" s="3" customFormat="1" spans="1:13">
-      <c r="A31" s="20">
+      <c r="A31" s="19">
         <v>31</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="22" t="s">
+      <c r="D31" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="F31" s="38">
+      <c r="F31" s="35">
         <v>45906</v>
       </c>
-      <c r="G31" s="38">
+      <c r="G31" s="35">
         <v>45910</v>
       </c>
-      <c r="H31" s="20" t="s">
+      <c r="H31" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="I31" s="20" t="s">
+      <c r="I31" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J31" s="22" t="s">
+      <c r="J31" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20" t="s">
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="32" s="5" customFormat="1" spans="1:13">
-      <c r="A32" s="28">
+      <c r="A32" s="27">
         <v>32</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="29" t="s">
+      <c r="D32" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="F32" s="46">
+      <c r="F32" s="42">
         <v>45903</v>
       </c>
-      <c r="G32" s="46">
+      <c r="G32" s="42">
         <v>45915</v>
       </c>
-      <c r="H32" s="28">
+      <c r="H32" s="27">
         <v>20263304452</v>
       </c>
-      <c r="I32" s="28" t="s">
+      <c r="I32" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="J32" s="29" t="s">
+      <c r="J32" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:13">
-      <c r="A33" s="11">
+      <c r="A33" s="10">
         <v>33</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="49" t="s">
+      <c r="D33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="47">
+      <c r="F33" s="43">
         <v>45905</v>
       </c>
-      <c r="G33" s="47">
+      <c r="G33" s="43">
         <v>45909</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="10">
         <v>20263311417</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J33" s="49" t="s">
+      <c r="J33" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="K33" s="11" t="s">
+      <c r="K33" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="L33" s="11" t="s">
+      <c r="L33" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="M33" s="11"/>
+      <c r="M33" s="10"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="35">
-        <v>34</v>
-      </c>
-      <c r="B34" s="35" t="s">
+      <c r="A34" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="D34" s="35"/>
-      <c r="E34" s="42" t="s">
+      <c r="C34" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="F34" s="37">
+      <c r="D34" s="32"/>
+      <c r="E34" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" s="34">
         <v>45880</v>
       </c>
-      <c r="G34" s="37">
+      <c r="G34" s="34">
         <v>45910</v>
       </c>
-      <c r="H34" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="I34" s="35" t="s">
+      <c r="H34" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="I34" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="J34" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="35"/>
+      <c r="J34" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:13">
-      <c r="A35" s="11">
+      <c r="A35" s="10">
         <v>35</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C35" s="11" t="s">
+      <c r="B35" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="D35" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11">
+      <c r="C35" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10">
         <v>202608849</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J35" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="K35" s="11" t="s">
+      <c r="J35" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="K35" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="L35" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="M35" s="11"/>
+      <c r="L35" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="M35" s="10"/>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:13">
-      <c r="A36" s="20">
+      <c r="A36" s="19">
         <v>36</v>
       </c>
-      <c r="B36" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="C36" s="20" t="s">
+      <c r="B36" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="D36" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="22" t="s">
+      <c r="C36" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="F36" s="38">
+      <c r="D36" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="F36" s="35">
         <v>45904</v>
       </c>
-      <c r="G36" s="38">
+      <c r="G36" s="35">
         <v>45912</v>
       </c>
-      <c r="H36" s="20">
+      <c r="H36" s="19">
         <v>20263327091</v>
       </c>
-      <c r="I36" s="20" t="s">
+      <c r="I36" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J36" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
+      <c r="J36" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:13">
-      <c r="A37" s="11">
+      <c r="A37" s="10">
         <v>37</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" s="11" t="s">
+      <c r="B37" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11" t="s">
+      <c r="C37" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J37" s="48" t="s">
-        <v>148</v>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
+      <c r="J37" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
     </row>
     <row r="38" s="5" customFormat="1" spans="1:13">
-      <c r="A38" s="28">
+      <c r="A38" s="27">
         <v>38</v>
       </c>
-      <c r="B38" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="C38" s="28" t="s">
+      <c r="B38" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="29" t="s">
+      <c r="C38" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="F38" s="46">
+      <c r="D38" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F38" s="42">
         <v>45904</v>
       </c>
-      <c r="G38" s="46">
+      <c r="G38" s="42">
         <v>45913</v>
       </c>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
+      <c r="K38" s="27"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="27"/>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="35">
+      <c r="A39" s="32">
         <v>39</v>
       </c>
-      <c r="B39" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="C39" s="43" t="s">
+      <c r="B39" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="D39" s="43" t="s">
+      <c r="D39" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="E39" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="F39" s="45">
+      <c r="E39" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="F39" s="41">
         <v>45909</v>
       </c>
-      <c r="G39" s="45">
+      <c r="G39" s="41">
         <v>45915</v>
       </c>
-      <c r="H39" s="43">
+      <c r="H39" s="39">
         <v>202602944</v>
       </c>
-      <c r="I39" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="J39" s="43"/>
-      <c r="K39" s="43"/>
-      <c r="L39" s="43"/>
-      <c r="M39" s="43"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="8"/>
+      <c r="I39" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:13">
-      <c r="A40" s="11">
+      <c r="A40" s="10">
         <v>40</v>
       </c>
-      <c r="B40" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C40" s="11" t="s">
+      <c r="B40" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="F40" s="47">
+      <c r="D40" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="F40" s="43">
         <v>45908</v>
       </c>
-      <c r="G40" s="47">
+      <c r="G40" s="43">
         <v>45921</v>
       </c>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-    </row>
-    <row r="41" s="8" customFormat="1" spans="1:15">
-      <c r="A41" s="35">
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+    </row>
+    <row r="41" s="7" customFormat="1" spans="1:15">
+      <c r="A41" s="32">
         <v>41</v>
       </c>
-      <c r="B41" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="C41" s="35" t="s">
+      <c r="B41" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="D41" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="36" t="s">
+      <c r="C41" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="F41" s="37">
+      <c r="D41" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="F41" s="34">
         <v>45910</v>
       </c>
-      <c r="G41" s="37">
+      <c r="G41" s="34">
         <v>45916</v>
       </c>
-      <c r="H41" s="35" t="s">
+      <c r="H41" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="35" t="s">
+      <c r="I41" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="J41" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="K41" s="35"/>
-      <c r="L41" s="35"/>
-      <c r="M41" s="35"/>
+      <c r="J41" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="K41" s="32"/>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32"/>
       <c r="N41"/>
       <c r="O41"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="35">
+      <c r="A42" s="32">
         <v>42</v>
       </c>
-      <c r="B42" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="C42" s="35" t="s">
+      <c r="B42" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="D42" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" s="42" t="s">
+      <c r="C42" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="F42" s="37">
+      <c r="D42" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="F42" s="34">
         <v>45909</v>
       </c>
-      <c r="G42" s="37">
+      <c r="G42" s="34">
         <v>45922</v>
       </c>
-      <c r="H42" s="35">
+      <c r="H42" s="32">
         <v>202601040</v>
       </c>
-      <c r="I42" s="35" t="s">
+      <c r="I42" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="J42" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="K42" s="35"/>
-      <c r="L42" s="35"/>
-      <c r="M42" s="35"/>
+      <c r="J42" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:13">
-      <c r="A43" s="11">
+      <c r="A43" s="10">
         <v>43</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="C43" s="11" t="s">
+      <c r="B43" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C43" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11">
+      <c r="D43" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10">
         <v>20263309395</v>
       </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="10" t="s">
         <v>18</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
+        <v>168</v>
+      </c>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="35">
+      <c r="A44" s="32">
         <v>44</v>
       </c>
-      <c r="B44" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="C44" s="35" t="s">
+      <c r="B44" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="D44" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="35"/>
-      <c r="K44" s="35"/>
-      <c r="L44" s="35"/>
-      <c r="M44" s="35" t="s">
+      <c r="D44" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" s="3" customFormat="1" spans="1:13">
+      <c r="A45" s="19">
+        <v>45</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="F45" s="35">
+        <v>45912</v>
+      </c>
+      <c r="G45" s="35">
+        <v>45915</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="I45" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+    </row>
+    <row r="46" s="6" customFormat="1" spans="1:13">
+      <c r="A46" s="36">
+        <v>46</v>
+      </c>
+      <c r="B46" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="F46" s="46">
+        <v>45915</v>
+      </c>
+      <c r="G46" s="46">
+        <v>45920</v>
+      </c>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="36"/>
+      <c r="M46" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="1:13">
+      <c r="A47" s="10">
+        <v>47</v>
+      </c>
+      <c r="B47" s="10" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="45" s="3" customFormat="1" spans="1:13">
-      <c r="A45" s="20">
-        <v>45</v>
-      </c>
-      <c r="B45" s="20" t="s">
+      <c r="C47" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C45" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="F45" s="38">
-        <v>45912</v>
-      </c>
-      <c r="G45" s="38">
+    </row>
+    <row r="48" s="1" customFormat="1" spans="1:13">
+      <c r="A48" s="10">
+        <v>48</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="32">
+        <v>49</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="32">
+        <v>50</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="F50" s="34">
+        <v>45904</v>
+      </c>
+      <c r="G50" s="34">
         <v>45915</v>
       </c>
-      <c r="H45" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I45" s="20" t="s">
+      <c r="H50" s="32">
+        <v>2513269</v>
+      </c>
+      <c r="I50" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="J45" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-    </row>
-    <row r="46" s="7" customFormat="1" spans="1:13">
-      <c r="A46" s="39">
-        <v>46</v>
-      </c>
-      <c r="B46" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="C46" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="D46" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="E46" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="F46" s="50">
-        <v>45915</v>
-      </c>
-      <c r="G46" s="50">
-        <v>45920</v>
-      </c>
-      <c r="H46" s="39"/>
-      <c r="I46" s="39"/>
-      <c r="J46" s="39"/>
-      <c r="K46" s="39"/>
-      <c r="L46" s="39"/>
-      <c r="M46" s="39" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" spans="1:13">
-      <c r="A47" s="11">
-        <v>47</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="12"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" spans="1:13">
-      <c r="A48" s="11">
-        <v>48</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C48" s="11" t="s">
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="32">
+        <v>51</v>
+      </c>
+      <c r="B51" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="C51" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="D48" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I48" s="11" t="s">
+      <c r="D51" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I51" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-    </row>
-    <row r="49" spans="1:13">
-      <c r="A49" s="35">
-        <v>49</v>
-      </c>
-      <c r="B49" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C49" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="D49" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="35"/>
-      <c r="F49" s="35"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J49" s="42" t="s">
-        <v>180</v>
-      </c>
-      <c r="K49" s="35"/>
-      <c r="L49" s="35"/>
-      <c r="M49" s="35"/>
-    </row>
-    <row r="50" spans="1:13">
-      <c r="A50" s="35">
-        <v>50</v>
-      </c>
-      <c r="B50" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="C50" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="D50" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="F50" s="37">
-        <v>45904</v>
-      </c>
-      <c r="G50" s="37">
-        <v>45915</v>
-      </c>
-      <c r="H50" s="35">
-        <v>2513269</v>
-      </c>
-      <c r="I50" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" s="35"/>
-      <c r="K50" s="35"/>
-      <c r="L50" s="35"/>
-      <c r="M50" s="35"/>
-    </row>
-    <row r="51" spans="1:13">
-      <c r="A51" s="35">
-        <v>51</v>
-      </c>
-      <c r="B51" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="C51" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="D51" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" s="35"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="35"/>
-      <c r="H51" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J51" s="36" t="s">
-        <v>184</v>
-      </c>
-      <c r="K51" s="35"/>
-      <c r="L51" s="35"/>
-      <c r="M51" s="35"/>
+      <c r="J51" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="35"/>
-      <c r="B52" s="35"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="35"/>
-      <c r="J52" s="35"/>
-      <c r="K52" s="35"/>
-      <c r="L52" s="35"/>
-      <c r="M52" s="35"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="35"/>
-      <c r="B53" s="35"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="35"/>
-      <c r="I53" s="35"/>
-      <c r="J53" s="35"/>
-      <c r="K53" s="35"/>
-      <c r="L53" s="35"/>
-      <c r="M53" s="35"/>
+      <c r="A53" s="32"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="35"/>
-      <c r="B54" s="35"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="35"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="35"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="35"/>
-      <c r="J54" s="35"/>
-      <c r="K54" s="35"/>
-      <c r="L54" s="35"/>
-      <c r="M54" s="35"/>
+      <c r="A54" s="32"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="32"/>
+      <c r="L54" s="32"/>
+      <c r="M54" s="32"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="35"/>
-      <c r="B55" s="35"/>
-      <c r="C55" s="35"/>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="35"/>
-      <c r="I55" s="35"/>
-      <c r="J55" s="35"/>
-      <c r="K55" s="35"/>
-      <c r="L55" s="35"/>
-      <c r="M55" s="35"/>
+      <c r="A55" s="32"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="35"/>
-      <c r="B56" s="35"/>
-      <c r="C56" s="35"/>
-      <c r="D56" s="35"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="35"/>
-      <c r="I56" s="35"/>
-      <c r="J56" s="35"/>
-      <c r="K56" s="35"/>
-      <c r="L56" s="35"/>
-      <c r="M56" s="35"/>
+      <c r="A56" s="32"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="35"/>
-      <c r="B57" s="35"/>
-      <c r="C57" s="35"/>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="35"/>
-      <c r="I57" s="35"/>
-      <c r="J57" s="35"/>
-      <c r="K57" s="35"/>
-      <c r="L57" s="35"/>
-      <c r="M57" s="35"/>
+      <c r="A57" s="32"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
+      <c r="L57" s="32"/>
+      <c r="M57" s="32"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="35"/>
-      <c r="B58" s="35"/>
-      <c r="C58" s="35"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="35"/>
-      <c r="J58" s="35"/>
-      <c r="K58" s="35"/>
-      <c r="L58" s="35"/>
-      <c r="M58" s="35"/>
+      <c r="A58" s="32"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="35"/>
-      <c r="B59" s="35"/>
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="35"/>
-      <c r="I59" s="35"/>
-      <c r="J59" s="35"/>
-      <c r="K59" s="35"/>
-      <c r="L59" s="35"/>
-      <c r="M59" s="35"/>
+      <c r="A59" s="32"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="32"/>
+      <c r="L59" s="32"/>
+      <c r="M59" s="32"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="35"/>
-      <c r="B60" s="35"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="35"/>
-      <c r="J60" s="35"/>
-      <c r="K60" s="35"/>
-      <c r="L60" s="35"/>
-      <c r="M60" s="35"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="32"/>
+      <c r="I60" s="32"/>
+      <c r="J60" s="32"/>
+      <c r="K60" s="32"/>
+      <c r="L60" s="32"/>
+      <c r="M60" s="32"/>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="35"/>
-      <c r="B61" s="35"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="35"/>
-      <c r="K61" s="35"/>
-      <c r="L61" s="35"/>
-      <c r="M61" s="35"/>
+      <c r="A61" s="32"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32"/>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="35"/>
-      <c r="B62" s="35"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="35"/>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="35"/>
-      <c r="J62" s="35"/>
-      <c r="K62" s="35"/>
-      <c r="L62" s="35"/>
-      <c r="M62" s="35"/>
+      <c r="A62" s="32"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
+      <c r="J62" s="32"/>
+      <c r="K62" s="32"/>
+      <c r="L62" s="32"/>
+      <c r="M62" s="32"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="35"/>
-      <c r="B63" s="35"/>
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35"/>
-      <c r="I63" s="35"/>
-      <c r="J63" s="35"/>
-      <c r="K63" s="35"/>
-      <c r="L63" s="35"/>
-      <c r="M63" s="35"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
+      <c r="J63" s="32"/>
+      <c r="K63" s="32"/>
+      <c r="L63" s="32"/>
+      <c r="M63" s="32"/>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="35"/>
-      <c r="B64" s="35"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="35"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="35"/>
-      <c r="J64" s="35"/>
-      <c r="K64" s="35"/>
-      <c r="L64" s="35"/>
-      <c r="M64" s="35"/>
+      <c r="A64" s="32"/>
+      <c r="B64" s="32"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="32"/>
+      <c r="K64" s="32"/>
+      <c r="L64" s="32"/>
+      <c r="M64" s="32"/>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="35"/>
-      <c r="B65" s="35"/>
-      <c r="C65" s="35"/>
-      <c r="D65" s="35"/>
-      <c r="E65" s="35"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="35"/>
-      <c r="I65" s="35"/>
-      <c r="J65" s="35"/>
-      <c r="K65" s="35"/>
-      <c r="L65" s="35"/>
-      <c r="M65" s="35"/>
+      <c r="A65" s="32"/>
+      <c r="B65" s="32"/>
+      <c r="C65" s="32"/>
+      <c r="D65" s="32"/>
+      <c r="E65" s="32"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
+      <c r="J65" s="32"/>
+      <c r="K65" s="32"/>
+      <c r="L65" s="32"/>
+      <c r="M65" s="32"/>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="35"/>
-      <c r="B66" s="35"/>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="35"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="35"/>
-      <c r="I66" s="35"/>
-      <c r="J66" s="35"/>
-      <c r="K66" s="35"/>
-      <c r="L66" s="35"/>
-      <c r="M66" s="35"/>
+      <c r="A66" s="32"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="32"/>
+      <c r="I66" s="32"/>
+      <c r="J66" s="32"/>
+      <c r="K66" s="32"/>
+      <c r="L66" s="32"/>
+      <c r="M66" s="32"/>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="35"/>
-      <c r="B67" s="35"/>
-      <c r="C67" s="35"/>
-      <c r="D67" s="35"/>
-      <c r="E67" s="35"/>
-      <c r="F67" s="35"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="35"/>
-      <c r="I67" s="35"/>
-      <c r="J67" s="35"/>
-      <c r="K67" s="35"/>
-      <c r="L67" s="35"/>
-      <c r="M67" s="35"/>
+      <c r="A67" s="32"/>
+      <c r="B67" s="32"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
+      <c r="L67" s="32"/>
+      <c r="M67" s="32"/>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="35"/>
-      <c r="B68" s="35"/>
-      <c r="C68" s="35"/>
-      <c r="D68" s="35"/>
-      <c r="E68" s="35"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="35"/>
-      <c r="I68" s="35"/>
-      <c r="J68" s="35"/>
-      <c r="K68" s="35"/>
-      <c r="L68" s="35"/>
-      <c r="M68" s="35"/>
+      <c r="A68" s="32"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
+      <c r="J68" s="32"/>
+      <c r="K68" s="32"/>
+      <c r="L68" s="32"/>
+      <c r="M68" s="32"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="35"/>
-      <c r="B69" s="35"/>
-      <c r="C69" s="35"/>
-      <c r="D69" s="35"/>
-      <c r="E69" s="35"/>
-      <c r="F69" s="35"/>
-      <c r="G69" s="35"/>
-      <c r="H69" s="35"/>
-      <c r="I69" s="35"/>
-      <c r="J69" s="35"/>
-      <c r="K69" s="35"/>
-      <c r="L69" s="35"/>
-      <c r="M69" s="35"/>
+      <c r="A69" s="32"/>
+      <c r="B69" s="32"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
+      <c r="J69" s="32"/>
+      <c r="K69" s="32"/>
+      <c r="L69" s="32"/>
+      <c r="M69" s="32"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="35"/>
-      <c r="B70" s="35"/>
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="35"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="35"/>
-      <c r="J70" s="35"/>
-      <c r="K70" s="35"/>
-      <c r="L70" s="35"/>
-      <c r="M70" s="35"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="32"/>
+      <c r="M70" s="32"/>
     </row>
   </sheetData>
   <hyperlinks>
